--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -1357,10 +1357,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122924906</v>
+        <v>122924072</v>
       </c>
       <c r="B7" t="n">
-        <v>56688</v>
+        <v>8441</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1373,29 +1373,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1405,14 +1406,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566411</v>
+        <v>566430</v>
       </c>
       <c r="R7" t="n">
-        <v>6584027</v>
+        <v>6584245</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1444,7 +1445,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1454,12 +1455,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>spillning i äldre hälimarksskog. Skogen är avverkningsanmäld.</t>
+          <t>Gnagspår på tallåga i hällmark</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1468,6 +1469,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1479,6 +1481,21 @@
       <c r="AI7" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1496,10 +1513,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122924072</v>
+        <v>122924906</v>
       </c>
       <c r="B8" t="n">
-        <v>8441</v>
+        <v>56688</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1512,30 +1529,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1545,14 +1561,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Öster om Höghäll, Slätthagen, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566430</v>
+        <v>566411</v>
       </c>
       <c r="R8" t="n">
-        <v>6584245</v>
+        <v>6584027</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1584,7 +1600,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1594,12 +1610,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gnagspår på tallåga i hällmark</t>
+          <t>spillning i äldre hälimarksskog. Skogen är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1608,7 +1624,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1620,21 +1635,6 @@
       <c r="AI8" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1650,6 +1650,1572 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123009266</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>566408</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6584004</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Hälmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123003959</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Björnsten, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>566582</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6584418</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Emelie Bergermark</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Emelie Bergermark</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123008173</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>566354</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6584152</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123008304</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>566374</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6584013</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på stående död tall.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123008823</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>566444</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6583992</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123003070</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56688</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Morfars trappa, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>566462</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6584262</v>
+      </c>
+      <c r="S14" t="n">
+        <v>14</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123010595</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lövlunda, Lövlunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>566008</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6583487</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123008919</v>
+      </c>
+      <c r="B16" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>566404</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6584083</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123011004</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lövlunda, Lövlunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>566010</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6583585</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Äldre barrskogsmiljö</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123007993</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Söder om Höghäll, Slätthagen, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>566400</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6584187</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123009148</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79384</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>566372</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6584091</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Substrat är gammal tallstubbe i hällmark.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122924063</v>
+        <v>122924036</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>105463</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -723,14 +723,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öster om Höghäll, Slätthagen, Srm</t>
+          <t>Sydost om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566588</v>
+        <v>566654</v>
       </c>
       <c r="R2" t="n">
-        <v>6584418</v>
+        <v>6584502</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,6 +781,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,7 +792,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Äldre barrskog.</t>
+          <t>Barrskog. Kontinutietsskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -809,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122924036</v>
+        <v>122924072</v>
       </c>
       <c r="B3" t="n">
-        <v>105463</v>
+        <v>8441</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,31 +826,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -857,14 +859,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sydost om Höghäll, Slätthagen, Srm</t>
+          <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566654</v>
+        <v>566430</v>
       </c>
       <c r="R3" t="n">
-        <v>6584502</v>
+        <v>6584245</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -896,7 +898,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -906,7 +908,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gnagspår på tallåga i hällmark</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,7 +933,22 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrskog. Kontinutietsskog</t>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -944,10 +966,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122925010</v>
+        <v>122924069</v>
       </c>
       <c r="B4" t="n">
-        <v>56688</v>
+        <v>95128</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,46 +982,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566430</v>
+        <v>566445</v>
       </c>
       <c r="R4" t="n">
-        <v>6584038</v>
+        <v>6584241</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1031,7 +1053,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1041,12 +1063,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spillning i äldre hällmarksskog. Skogen är avverkningsanmäld.</t>
+          <t>Växer under martallar på hällmark</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,6 +1077,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1065,7 +1088,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Hällmarksskog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1083,10 +1106,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122924069</v>
+        <v>122924063</v>
       </c>
       <c r="B5" t="n">
-        <v>95128</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1095,50 +1118,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566445</v>
+        <v>566588</v>
       </c>
       <c r="R5" t="n">
-        <v>6584241</v>
+        <v>6584418</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1183,18 +1206,12 @@
           <t>14:00</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Växer under martallar på hällmark</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1205,7 +1222,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Hällmarksskog.</t>
+          <t>Äldre barrskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1223,7 +1240,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122924806</v>
+        <v>122924906</v>
       </c>
       <c r="B6" t="n">
         <v>56688</v>
@@ -1275,10 +1292,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566416</v>
+        <v>566411</v>
       </c>
       <c r="R6" t="n">
-        <v>6584024</v>
+        <v>6584027</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1323,6 +1340,11 @@
           <t>12:30</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>spillning i äldre hälimarksskog. Skogen är avverkningsanmäld.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1339,7 +1361,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Hällmarksskog.</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1357,10 +1379,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122924072</v>
+        <v>122925010</v>
       </c>
       <c r="B7" t="n">
-        <v>8441</v>
+        <v>56688</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1373,30 +1395,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1406,14 +1427,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öster om Höghäll, Slätthagen, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>566430</v>
       </c>
       <c r="R7" t="n">
-        <v>6584245</v>
+        <v>6584038</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1445,7 +1466,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1455,12 +1476,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gnagspår på tallåga i hällmark</t>
+          <t>Spillning i äldre hällmarksskog. Skogen är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1469,7 +1490,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1481,21 +1501,6 @@
       <c r="AI7" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1513,7 +1518,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122924906</v>
+        <v>122924806</v>
       </c>
       <c r="B8" t="n">
         <v>56688</v>
@@ -1565,10 +1570,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566411</v>
+        <v>566416</v>
       </c>
       <c r="R8" t="n">
-        <v>6584027</v>
+        <v>6584024</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1613,11 +1618,6 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>spillning i äldre hälimarksskog. Skogen är avverkningsanmäld.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Hällmarksskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1652,10 +1652,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123009266</v>
+        <v>123008304</v>
       </c>
       <c r="B9" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1664,34 +1664,33 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1705,10 +1704,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566408</v>
+        <v>566374</v>
       </c>
       <c r="R9" t="n">
-        <v>6584004</v>
+        <v>6584013</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1753,13 +1752,17 @@
           <t>13:00</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på stående död tall.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1770,22 +1773,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Hälmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1803,7 +1791,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123003959</v>
+        <v>123011004</v>
       </c>
       <c r="B10" t="n">
         <v>57494</v>
@@ -1836,11 +1824,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
@@ -1848,20 +1832,24 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Lövlunda, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566582</v>
+        <v>566010</v>
       </c>
       <c r="R10" t="n">
-        <v>6584418</v>
+        <v>6583585</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1885,12 +1873,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1901,16 +1899,41 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre barrskogsmiljö</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2064,10 +2087,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123008304</v>
+        <v>123010595</v>
       </c>
       <c r="B12" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2076,50 +2099,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Lövlunda, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566374</v>
+        <v>566008</v>
       </c>
       <c r="R12" t="n">
-        <v>6584013</v>
+        <v>6583487</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2151,7 +2171,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2161,12 +2181,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska hackmärken på stående död tall.</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2175,6 +2190,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2186,6 +2202,21 @@
       <c r="AI12" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2354,10 +2385,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123003070</v>
+        <v>123008919</v>
       </c>
       <c r="B14" t="n">
-        <v>56688</v>
+        <v>8441</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2370,45 +2401,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Morfars trappa, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566462</v>
+        <v>566404</v>
       </c>
       <c r="R14" t="n">
-        <v>6584262</v>
+        <v>6584083</v>
       </c>
       <c r="S14" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2432,22 +2464,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2456,28 +2488,54 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123010595</v>
+        <v>123009148</v>
       </c>
       <c r="B15" t="n">
-        <v>8441</v>
+        <v>79384</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2486,47 +2544,45 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lövlunda, Lövlunda, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566008</v>
+        <v>566372</v>
       </c>
       <c r="R15" t="n">
-        <v>6583487</v>
+        <v>6584091</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2558,7 +2614,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2568,7 +2624,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Substrat är gammal tallstubbe i hällmark.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2621,7 +2682,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123008919</v>
+        <v>123009266</v>
       </c>
       <c r="B16" t="n">
         <v>8441</v>
@@ -2663,17 +2724,21 @@
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566404</v>
+        <v>566408</v>
       </c>
       <c r="R16" t="n">
-        <v>6584083</v>
+        <v>6584004</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2735,7 +2800,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Hälmarksskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2768,10 +2833,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123011004</v>
+        <v>123007993</v>
       </c>
       <c r="B17" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2780,33 +2845,34 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2816,14 +2882,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lövlunda, Lövlunda, Srm</t>
+          <t>Söder om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566010</v>
+        <v>566400</v>
       </c>
       <c r="R17" t="n">
-        <v>6583585</v>
+        <v>6584187</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2855,7 +2921,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2865,7 +2931,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2874,6 +2940,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2884,22 +2951,22 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Äldre barrskogsmiljö</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2917,10 +2984,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123007993</v>
+        <v>123003959</v>
       </c>
       <c r="B18" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2929,54 +2996,53 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Slätthagen, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566400</v>
+        <v>566582</v>
       </c>
       <c r="R18" t="n">
-        <v>6584187</v>
+        <v>6584418</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3000,22 +3066,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3024,54 +3080,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123009148</v>
+        <v>123033899</v>
       </c>
       <c r="B19" t="n">
-        <v>79384</v>
+        <v>5173</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3080,48 +3110,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566372</v>
+        <v>566802</v>
       </c>
       <c r="R19" t="n">
-        <v>6584091</v>
+        <v>6584534</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3145,27 +3177,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Substrat är gammal tallstubbe i hällmark.</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3178,43 +3195,593 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123050079</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Björnsten, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>566634</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6584453</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
           <t>Michael Lander</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>Michael Lander</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123003070</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56688</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Morfars trappa, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>566462</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6584262</v>
+      </c>
+      <c r="S21" t="n">
+        <v>14</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anja Hynynen, Emelie Bergermark</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>123033108</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97311</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Björnsten, Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>566666</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6584456</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anja Hynynen, Emelie Bergermark</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>123034480</v>
+      </c>
+      <c r="B23" t="n">
+        <v>8430</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Farfars trappa, Srm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>566456</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6584284</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>123034725</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Farfars trappa, Srm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>566550</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6584397</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2833,10 +2833,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123007993</v>
+        <v>123003959</v>
       </c>
       <c r="B17" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2845,54 +2845,53 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Slätthagen, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566400</v>
+        <v>566582</v>
       </c>
       <c r="R17" t="n">
-        <v>6584187</v>
+        <v>6584418</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2916,22 +2915,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2940,54 +2929,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123003959</v>
+        <v>123007993</v>
       </c>
       <c r="B18" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2996,53 +2959,54 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Söder om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566582</v>
+        <v>566400</v>
       </c>
       <c r="R18" t="n">
-        <v>6584418</v>
+        <v>6584187</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3066,12 +3030,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3080,18 +3054,44 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3561,10 +3561,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123034480</v>
+        <v>123034725</v>
       </c>
       <c r="B23" t="n">
-        <v>8430</v>
+        <v>5173</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3577,21 +3577,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566456</v>
+        <v>566550</v>
       </c>
       <c r="R23" t="n">
-        <v>6584284</v>
+        <v>6584397</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3673,10 +3673,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123034725</v>
+        <v>123080289</v>
       </c>
       <c r="B24" t="n">
-        <v>5173</v>
+        <v>98357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3685,50 +3685,45 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Farfars trappa, Srm</t>
+          <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566550</v>
+        <v>566632</v>
       </c>
       <c r="R24" t="n">
-        <v>6584397</v>
+        <v>6584457</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3752,12 +3747,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3770,18 +3775,456 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Äldre barrskog.</t>
+        </is>
+      </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>123077638</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Öster om Höghäll, Slätthagen, Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>566640</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6584477</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Växer längs den gamla kyrkstigen i äldre barrskog.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Äldre barrskogsmiljö</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>123079585</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Öster om Höghäll, Slätthagen, Srm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>566632</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6584462</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Växer i mossrik äldre barrskog.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>123080901</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Öster om Höghäll, Slätthagen, Srm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>566636</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6584458</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Knärot i äldre barrskog med vinterståndare.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Äldre barrskog. Kontinuitetsskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -2833,10 +2833,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123003959</v>
+        <v>123007993</v>
       </c>
       <c r="B17" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2845,53 +2845,54 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Söder om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566582</v>
+        <v>566400</v>
       </c>
       <c r="R17" t="n">
-        <v>6584418</v>
+        <v>6584187</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2915,12 +2916,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2929,28 +2940,54 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123007993</v>
+        <v>123003959</v>
       </c>
       <c r="B18" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2959,54 +2996,53 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Slätthagen, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566400</v>
+        <v>566582</v>
       </c>
       <c r="R18" t="n">
-        <v>6584187</v>
+        <v>6584418</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3030,22 +3066,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3054,44 +3080,18 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122924036</v>
+        <v>122924072</v>
       </c>
       <c r="B2" t="n">
-        <v>105463</v>
+        <v>8441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -723,14 +724,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sydost om Höghäll, Slätthagen, Srm</t>
+          <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566654</v>
+        <v>566430</v>
       </c>
       <c r="R2" t="n">
-        <v>6584502</v>
+        <v>6584245</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,7 +763,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +773,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gnagspår på tallåga i hällmark</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +798,22 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Barrskog. Kontinutietsskog</t>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,10 +831,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122924072</v>
+        <v>122924069</v>
       </c>
       <c r="B3" t="n">
-        <v>8441</v>
+        <v>95136</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,47 +847,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566430</v>
+        <v>566445</v>
       </c>
       <c r="R3" t="n">
-        <v>6584245</v>
+        <v>6584241</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -913,7 +933,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gnagspår på tallåga i hällmark</t>
+          <t>Växer under martallar på hällmark</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -933,22 +953,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Hällmarksskog.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -966,10 +971,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122924069</v>
+        <v>122924063</v>
       </c>
       <c r="B4" t="n">
-        <v>95128</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -978,50 +983,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566445</v>
+        <v>566588</v>
       </c>
       <c r="R4" t="n">
-        <v>6584241</v>
+        <v>6584418</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1066,18 +1071,12 @@
           <t>14:00</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Växer under martallar på hällmark</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1088,7 +1087,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Hällmarksskog.</t>
+          <t>Äldre barrskog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1106,10 +1105,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122924063</v>
+        <v>122924906</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>56688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1118,25 +1117,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1144,7 +1143,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1154,14 +1153,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öster om Höghäll, Slätthagen, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566588</v>
+        <v>566411</v>
       </c>
       <c r="R5" t="n">
-        <v>6584418</v>
+        <v>6584027</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1193,7 +1192,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1203,7 +1202,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>spillning i äldre hälimarksskog. Skogen är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1222,7 +1226,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Äldre barrskog.</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1240,10 +1244,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122924906</v>
+        <v>122924036</v>
       </c>
       <c r="B6" t="n">
-        <v>56688</v>
+        <v>105471</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1256,31 +1260,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1288,14 +1292,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Sydost om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566411</v>
+        <v>566654</v>
       </c>
       <c r="R6" t="n">
-        <v>6584027</v>
+        <v>6584502</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1327,7 +1331,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1337,12 +1341,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>spillning i äldre hälimarksskog. Skogen är avverkningsanmäld.</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1351,6 +1350,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Barrskog. Kontinutietsskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1379,7 +1379,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122925010</v>
+        <v>122924806</v>
       </c>
       <c r="B7" t="n">
         <v>56688</v>
@@ -1417,7 +1417,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566430</v>
+        <v>566416</v>
       </c>
       <c r="R7" t="n">
-        <v>6584038</v>
+        <v>6584024</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1479,11 +1479,6 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spillning i äldre hällmarksskog. Skogen är avverkningsanmäld.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1500,7 +1495,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Hällmarksskog.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1518,7 +1513,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122924806</v>
+        <v>122925010</v>
       </c>
       <c r="B8" t="n">
         <v>56688</v>
@@ -1556,7 +1551,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1570,10 +1565,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566416</v>
+        <v>566430</v>
       </c>
       <c r="R8" t="n">
-        <v>6584024</v>
+        <v>6584038</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1618,6 +1613,11 @@
           <t>12:30</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spillning i äldre hällmarksskog. Skogen är avverkningsanmäld.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Hällmarksskog.</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1652,10 +1652,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123008304</v>
+        <v>123009266</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1664,33 +1664,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1704,10 +1705,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566374</v>
+        <v>566408</v>
       </c>
       <c r="R9" t="n">
-        <v>6584013</v>
+        <v>6584004</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1752,17 +1753,13 @@
           <t>13:00</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska hackmärken på stående död tall.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1773,7 +1770,22 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Hälmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1791,10 +1803,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123011004</v>
+        <v>123010595</v>
       </c>
       <c r="B10" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1803,50 +1815,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lövlunda, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566010</v>
+        <v>566008</v>
       </c>
       <c r="R10" t="n">
-        <v>6583585</v>
+        <v>6583487</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1878,7 +1887,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1888,7 +1897,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1897,6 +1906,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1907,22 +1917,22 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre barrskogsmiljö</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1940,10 +1950,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123008173</v>
+        <v>123003959</v>
       </c>
       <c r="B11" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1952,50 +1962,53 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566354</v>
+        <v>566582</v>
       </c>
       <c r="R11" t="n">
-        <v>6584152</v>
+        <v>6584418</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2019,22 +2032,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2043,54 +2046,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123010595</v>
+        <v>123008823</v>
       </c>
       <c r="B12" t="n">
-        <v>8441</v>
+        <v>5173</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2103,21 +2080,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2126,20 +2103,24 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lövlunda, Lövlunda, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566008</v>
+        <v>566444</v>
       </c>
       <c r="R12" t="n">
-        <v>6583487</v>
+        <v>6583992</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2171,7 +2152,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2181,7 +2162,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2206,17 +2187,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2234,10 +2215,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123008823</v>
+        <v>123011004</v>
       </c>
       <c r="B13" t="n">
-        <v>5173</v>
+        <v>57494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2246,34 +2227,33 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2283,14 +2263,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Lövlunda, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566444</v>
+        <v>566010</v>
       </c>
       <c r="R13" t="n">
-        <v>6583992</v>
+        <v>6583585</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2322,7 +2302,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2332,7 +2312,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2341,7 +2321,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2352,7 +2331,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Äldre barrskogsmiljö</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2385,7 +2364,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123008919</v>
+        <v>123007993</v>
       </c>
       <c r="B14" t="n">
         <v>8441</v>
@@ -2427,17 +2406,21 @@
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Söder om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566404</v>
+        <v>566400</v>
       </c>
       <c r="R14" t="n">
-        <v>6584083</v>
+        <v>6584187</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2469,7 +2452,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2479,7 +2462,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2532,10 +2515,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123009148</v>
+        <v>123008173</v>
       </c>
       <c r="B15" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2544,32 +2527,34 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2579,10 +2564,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566372</v>
+        <v>566354</v>
       </c>
       <c r="R15" t="n">
-        <v>6584091</v>
+        <v>6584152</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2614,7 +2599,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2624,12 +2609,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Substrat är gammal tallstubbe i hällmark.</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2682,7 +2662,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123009266</v>
+        <v>123008919</v>
       </c>
       <c r="B16" t="n">
         <v>8441</v>
@@ -2724,21 +2704,17 @@
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566408</v>
+        <v>566404</v>
       </c>
       <c r="R16" t="n">
-        <v>6584004</v>
+        <v>6584083</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2800,7 +2776,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Hälmarksskog</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2833,10 +2809,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123007993</v>
+        <v>123008304</v>
       </c>
       <c r="B17" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2845,34 +2821,33 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2882,14 +2857,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Slätthagen, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566400</v>
+        <v>566374</v>
       </c>
       <c r="R17" t="n">
-        <v>6584187</v>
+        <v>6584013</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2921,7 +2896,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2931,7 +2906,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på stående död tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2940,7 +2920,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2952,21 +2931,6 @@
       <c r="AI17" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2984,10 +2948,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123003959</v>
+        <v>123009148</v>
       </c>
       <c r="B18" t="n">
-        <v>57494</v>
+        <v>79384</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -3000,49 +2964,44 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566582</v>
+        <v>566372</v>
       </c>
       <c r="R18" t="n">
-        <v>6584418</v>
+        <v>6584091</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3066,12 +3025,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Substrat är gammal tallstubbe i hällmark.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3080,28 +3054,54 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123033899</v>
+        <v>123033108</v>
       </c>
       <c r="B19" t="n">
-        <v>5173</v>
+        <v>97319</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3114,32 +3114,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3147,10 +3142,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566802</v>
+        <v>566666</v>
       </c>
       <c r="R19" t="n">
-        <v>6584534</v>
+        <v>6584456</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3203,7 +3198,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Anja Hynynen, Emelie Bergermark</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3213,7 +3208,7 @@
         <v>123050079</v>
       </c>
       <c r="B20" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3454,10 +3449,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123033108</v>
+        <v>123034725</v>
       </c>
       <c r="B22" t="n">
-        <v>97311</v>
+        <v>5173</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3470,38 +3465,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Farfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566666</v>
+        <v>566550</v>
       </c>
       <c r="R22" t="n">
-        <v>6584456</v>
+        <v>6584397</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3554,14 +3554,14 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anja Hynynen, Emelie Bergermark</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123034725</v>
+        <v>123033899</v>
       </c>
       <c r="B23" t="n">
         <v>5173</v>
@@ -3606,14 +3606,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Farfars trappa, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566550</v>
+        <v>566802</v>
       </c>
       <c r="R23" t="n">
-        <v>6584397</v>
+        <v>6584534</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3676,7 +3676,7 @@
         <v>123080289</v>
       </c>
       <c r="B24" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123077638</v>
+        <v>123079585</v>
       </c>
       <c r="B25" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3852,13 +3852,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566640</v>
+        <v>566632</v>
       </c>
       <c r="R25" t="n">
-        <v>6584477</v>
+        <v>6584462</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Växer längs den gamla kyrkstigen i äldre barrskog.</t>
+          <t>Växer i mossrik äldre barrskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Äldre barrskogsmiljö</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3940,10 +3940,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123079585</v>
+        <v>123077638</v>
       </c>
       <c r="B26" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3992,13 +3992,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566632</v>
+        <v>566640</v>
       </c>
       <c r="R26" t="n">
-        <v>6584462</v>
+        <v>6584477</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Växer i mossrik äldre barrskog.</t>
+          <t>Växer längs den gamla kyrkstigen i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskogsmiljö</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4083,7 +4083,7 @@
         <v>123080901</v>
       </c>
       <c r="B27" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1803,10 +1803,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123010595</v>
+        <v>123003959</v>
       </c>
       <c r="B10" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1815,50 +1815,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lövlunda, Lövlunda, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566008</v>
+        <v>566582</v>
       </c>
       <c r="R10" t="n">
-        <v>6583487</v>
+        <v>6584418</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1882,22 +1885,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1906,54 +1899,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123003959</v>
+        <v>123010595</v>
       </c>
       <c r="B11" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1962,53 +1929,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Lövlunda, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566582</v>
+        <v>566008</v>
       </c>
       <c r="R11" t="n">
-        <v>6584418</v>
+        <v>6583487</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2032,12 +1996,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2046,18 +2020,44 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123008304</v>
+        <v>123009148</v>
       </c>
       <c r="B17" t="n">
-        <v>57494</v>
+        <v>79384</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2825,46 +2825,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566374</v>
+        <v>566372</v>
       </c>
       <c r="R17" t="n">
-        <v>6584013</v>
+        <v>6584091</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2911,7 +2906,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska hackmärken på stående död tall.</t>
+          <t>Substrat är gammal tallstubbe i hällmark.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2920,6 +2915,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2931,6 +2927,21 @@
       <c r="AI17" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2948,10 +2959,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123009148</v>
+        <v>123008304</v>
       </c>
       <c r="B18" t="n">
-        <v>79384</v>
+        <v>57494</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2964,41 +2975,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566372</v>
+        <v>566374</v>
       </c>
       <c r="R18" t="n">
-        <v>6584091</v>
+        <v>6584013</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3045,7 +3061,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Substrat är gammal tallstubbe i hällmark.</t>
+          <t>Färska hackmärken på stående död tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3054,7 +3070,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -3066,21 +3081,6 @@
       <c r="AI18" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -4226,6 +4226,131 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>123185939</v>
+      </c>
+      <c r="B28" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lövlunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>566060</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6583553</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122924072</v>
+        <v>122924906</v>
       </c>
       <c r="B2" t="n">
-        <v>8441</v>
+        <v>56688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,30 +691,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -724,14 +723,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öster om Höghäll, Slätthagen, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566430</v>
+        <v>566411</v>
       </c>
       <c r="R2" t="n">
-        <v>6584245</v>
+        <v>6584027</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -763,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -773,12 +772,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Gnagspår på tallåga i hällmark</t>
+          <t>spillning i äldre hälimarksskog. Skogen är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +786,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -799,21 +797,6 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -831,10 +814,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122924069</v>
+        <v>122924072</v>
       </c>
       <c r="B3" t="n">
-        <v>95136</v>
+        <v>8441</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -847,46 +830,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566445</v>
+        <v>566430</v>
       </c>
       <c r="R3" t="n">
-        <v>6584241</v>
+        <v>6584245</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -933,7 +917,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Växer under martallar på hällmark</t>
+          <t>Gnagspår på tallåga i hällmark</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -953,7 +937,22 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Hällmarksskog.</t>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -971,10 +970,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122924063</v>
+        <v>122924036</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>105471</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -983,35 +982,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1019,14 +1018,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öster om Höghäll, Slätthagen, Srm</t>
+          <t>Sydost om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566588</v>
+        <v>566654</v>
       </c>
       <c r="R4" t="n">
-        <v>6584418</v>
+        <v>6584502</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1058,7 +1057,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1068,7 +1067,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1077,6 +1076,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Äldre barrskog.</t>
+          <t>Barrskog. Kontinutietsskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122924906</v>
+        <v>122924806</v>
       </c>
       <c r="B5" t="n">
         <v>56688</v>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566411</v>
+        <v>566416</v>
       </c>
       <c r="R5" t="n">
-        <v>6584027</v>
+        <v>6584024</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1205,11 +1205,6 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>spillning i äldre hälimarksskog. Skogen är avverkningsanmäld.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1226,7 +1221,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Hällmarksskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1244,10 +1239,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122924036</v>
+        <v>122925010</v>
       </c>
       <c r="B6" t="n">
-        <v>105471</v>
+        <v>56688</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1260,31 +1255,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1292,14 +1287,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sydost om Höghäll, Slätthagen, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566654</v>
+        <v>566430</v>
       </c>
       <c r="R6" t="n">
-        <v>6584502</v>
+        <v>6584038</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1331,7 +1326,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1341,7 +1336,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spillning i äldre hällmarksskog. Skogen är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1350,7 +1350,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1361,7 +1360,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrskog. Kontinutietsskog</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1379,10 +1378,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122924806</v>
+        <v>122924069</v>
       </c>
       <c r="B7" t="n">
-        <v>56688</v>
+        <v>95136</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1395,46 +1394,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566416</v>
+        <v>566445</v>
       </c>
       <c r="R7" t="n">
-        <v>6584024</v>
+        <v>6584241</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1466,7 +1465,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1476,7 +1475,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Växer under martallar på hällmark</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1485,6 +1489,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1513,10 +1518,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122925010</v>
+        <v>122924063</v>
       </c>
       <c r="B8" t="n">
-        <v>56688</v>
+        <v>57494</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1525,25 +1530,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1551,7 +1556,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1561,14 +1566,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566430</v>
+        <v>566588</v>
       </c>
       <c r="R8" t="n">
-        <v>6584038</v>
+        <v>6584418</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1600,7 +1605,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1610,12 +1615,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spillning i äldre hällmarksskog. Skogen är avverkningsanmäld.</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Äldre barrskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1652,7 +1652,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123009266</v>
+        <v>123007993</v>
       </c>
       <c r="B9" t="n">
         <v>8441</v>
@@ -1701,14 +1701,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Söder om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566408</v>
+        <v>566400</v>
       </c>
       <c r="R9" t="n">
-        <v>6584004</v>
+        <v>6584187</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Hälmarksskog</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1803,10 +1803,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123003959</v>
+        <v>123010595</v>
       </c>
       <c r="B10" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1815,53 +1815,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Lövlunda, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566582</v>
+        <v>566008</v>
       </c>
       <c r="R10" t="n">
-        <v>6584418</v>
+        <v>6583487</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1885,12 +1882,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1899,28 +1906,54 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123010595</v>
+        <v>123003959</v>
       </c>
       <c r="B11" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1929,50 +1962,53 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lövlunda, Lövlunda, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566008</v>
+        <v>566582</v>
       </c>
       <c r="R11" t="n">
-        <v>6583487</v>
+        <v>6584418</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1996,22 +2032,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2020,54 +2046,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123008823</v>
+        <v>123008919</v>
       </c>
       <c r="B12" t="n">
-        <v>5173</v>
+        <v>8441</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2080,21 +2080,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2103,24 +2103,20 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566444</v>
+        <v>566404</v>
       </c>
       <c r="R12" t="n">
-        <v>6583992</v>
+        <v>6584083</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2187,17 +2183,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2215,10 +2211,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123011004</v>
+        <v>123009266</v>
       </c>
       <c r="B13" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2227,33 +2223,34 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2263,14 +2260,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lövlunda, Lövlunda, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566010</v>
+        <v>566408</v>
       </c>
       <c r="R13" t="n">
-        <v>6583585</v>
+        <v>6584004</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2302,7 +2299,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2312,7 +2309,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2321,6 +2318,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2331,22 +2329,22 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Äldre barrskogsmiljö</t>
+          <t>Hälmarksskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2364,10 +2362,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123007993</v>
+        <v>123011004</v>
       </c>
       <c r="B14" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2376,34 +2374,33 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2413,14 +2410,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Slätthagen, Srm</t>
+          <t>Lövlunda, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566400</v>
+        <v>566010</v>
       </c>
       <c r="R14" t="n">
-        <v>6584187</v>
+        <v>6583585</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2452,7 +2449,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2462,7 +2459,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2471,7 +2468,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2482,22 +2478,22 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Äldre barrskogsmiljö</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2515,10 +2511,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123008173</v>
+        <v>123009148</v>
       </c>
       <c r="B15" t="n">
-        <v>8441</v>
+        <v>79384</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2527,34 +2523,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2564,10 +2558,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566354</v>
+        <v>566372</v>
       </c>
       <c r="R15" t="n">
-        <v>6584152</v>
+        <v>6584091</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2599,7 +2593,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2609,7 +2603,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Substrat är gammal tallstubbe i hällmark.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2662,10 +2661,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123008919</v>
+        <v>123008304</v>
       </c>
       <c r="B16" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2674,47 +2673,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566404</v>
+        <v>566374</v>
       </c>
       <c r="R16" t="n">
-        <v>6584083</v>
+        <v>6584013</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2759,13 +2761,17 @@
           <t>13:00</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på stående död tall.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2777,21 +2783,6 @@
       <c r="AI16" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2809,10 +2800,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123009148</v>
+        <v>123008173</v>
       </c>
       <c r="B17" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2821,32 +2812,34 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2856,10 +2849,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566372</v>
+        <v>566354</v>
       </c>
       <c r="R17" t="n">
-        <v>6584091</v>
+        <v>6584152</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2891,7 +2884,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2901,12 +2894,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Substrat är gammal tallstubbe i hällmark.</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2959,10 +2947,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123008304</v>
+        <v>123008823</v>
       </c>
       <c r="B18" t="n">
-        <v>57494</v>
+        <v>5173</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2971,33 +2959,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -3011,10 +3000,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566374</v>
+        <v>566444</v>
       </c>
       <c r="R18" t="n">
-        <v>6584013</v>
+        <v>6583992</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3059,17 +3048,13 @@
           <t>13:00</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska hackmärken på stående död tall.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -3081,6 +3066,21 @@
       <c r="AI18" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3098,10 +3098,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123033108</v>
+        <v>123050079</v>
       </c>
       <c r="B19" t="n">
-        <v>97319</v>
+        <v>98365</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3110,29 +3110,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -3142,13 +3150,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566666</v>
+        <v>566634</v>
       </c>
       <c r="R19" t="n">
-        <v>6584456</v>
+        <v>6584453</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3172,12 +3180,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3186,29 +3204,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anja Hynynen, Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123050079</v>
+        <v>123034725</v>
       </c>
       <c r="B20" t="n">
-        <v>98365</v>
+        <v>5173</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3217,53 +3234,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Farfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566634</v>
+        <v>566550</v>
       </c>
       <c r="R20" t="n">
-        <v>6584453</v>
+        <v>6584397</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3287,22 +3301,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3311,28 +3315,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123003070</v>
+        <v>123033899</v>
       </c>
       <c r="B21" t="n">
-        <v>56688</v>
+        <v>5173</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3345,45 +3350,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Morfars trappa, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566462</v>
+        <v>566802</v>
       </c>
       <c r="R21" t="n">
-        <v>6584262</v>
+        <v>6584534</v>
       </c>
       <c r="S21" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3410,27 +3416,18 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3442,17 +3439,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anja Hynynen, Emelie Bergermark</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123034725</v>
+        <v>123003070</v>
       </c>
       <c r="B22" t="n">
-        <v>5173</v>
+        <v>56688</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3465,46 +3462,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Farfars trappa, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566550</v>
+        <v>566462</v>
       </c>
       <c r="R22" t="n">
-        <v>6584397</v>
+        <v>6584262</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3531,18 +3527,27 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3554,17 +3559,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Anja Hynynen, Emelie Bergermark</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123033899</v>
+        <v>123033108</v>
       </c>
       <c r="B23" t="n">
-        <v>5173</v>
+        <v>97319</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3577,32 +3582,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566802</v>
+        <v>566666</v>
       </c>
       <c r="R23" t="n">
-        <v>6584534</v>
+        <v>6584456</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3666,14 +3666,14 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Anja Hynynen, Emelie Bergermark</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123080289</v>
+        <v>123077638</v>
       </c>
       <c r="B24" t="n">
         <v>98365</v>
@@ -3706,8 +3706,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3717,10 +3725,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566632</v>
+        <v>566640</v>
       </c>
       <c r="R24" t="n">
-        <v>6584457</v>
+        <v>6584477</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3752,7 +3760,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3762,7 +3770,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Växer längs den gamla kyrkstigen i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3782,7 +3795,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Äldre barrskog.</t>
+          <t>Äldre barrskogsmiljö</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3800,7 +3813,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123079585</v>
+        <v>123080289</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3833,16 +3846,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3855,10 +3860,10 @@
         <v>566632</v>
       </c>
       <c r="R25" t="n">
-        <v>6584462</v>
+        <v>6584457</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3898,11 +3903,6 @@
       <c r="AB25" t="inlineStr">
         <is>
           <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Växer i mossrik äldre barrskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskog.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3940,7 +3940,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123077638</v>
+        <v>123080901</v>
       </c>
       <c r="B26" t="n">
         <v>98365</v>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3983,19 +3983,27 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566640</v>
+        <v>566636</v>
       </c>
       <c r="R26" t="n">
-        <v>6584477</v>
+        <v>6584458</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4042,7 +4050,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Växer längs den gamla kyrkstigen i äldre barrskog.</t>
+          <t>Knärot i äldre barrskog med vinterståndare.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4062,7 +4070,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Äldre barrskogsmiljö</t>
+          <t>Äldre barrskog. Kontinuitetsskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4080,7 +4088,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123080901</v>
+        <v>123079585</v>
       </c>
       <c r="B27" t="n">
         <v>98365</v>
@@ -4115,7 +4123,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4123,30 +4131,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566636</v>
+        <v>566632</v>
       </c>
       <c r="R27" t="n">
-        <v>6584458</v>
+        <v>6584462</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Knärot i äldre barrskog med vinterståndare.</t>
+          <t>Växer i mossrik äldre barrskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Äldre barrskog. Kontinuitetsskog</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123185939</v>
+        <v>123232797</v>
       </c>
       <c r="B28" t="n">
-        <v>8441</v>
+        <v>8430</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4244,28 +4244,24 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -4277,17 +4273,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lövlunda, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566060</v>
+        <v>566699</v>
       </c>
       <c r="R28" t="n">
-        <v>6583553</v>
+        <v>6584476</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4311,22 +4307,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4335,21 +4331,495 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>123241264</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Björnsten, Srm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>566553</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6584351</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>123231344</v>
+      </c>
+      <c r="B30" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Björnsten, Srm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>566775</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6584532</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>123185939</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lövlunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>566060</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6583553</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
           <t>Michael Lander</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
+      <c r="AX31" t="inlineStr">
         <is>
           <t>Michael Lander</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>123236226</v>
+      </c>
+      <c r="B32" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Morfars trappa, Srm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>566409</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6583988</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4707,7 +4707,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123236226</v>
+        <v>123271947</v>
       </c>
       <c r="B32" t="n">
         <v>90952</v>
@@ -4783,19 +4783,9 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>16:52</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>16:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4820,6 +4810,122 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>123236226</v>
+      </c>
+      <c r="B33" t="n">
+        <v>90917</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Morfars trappa, Srm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>566409</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6583988</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122924906</v>
+        <v>122924069</v>
       </c>
       <c r="B2" t="n">
-        <v>56688</v>
+        <v>95136</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566411</v>
+        <v>566445</v>
       </c>
       <c r="R2" t="n">
-        <v>6584027</v>
+        <v>6584241</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>spillning i äldre hälimarksskog. Skogen är avverkningsanmäld.</t>
+          <t>Växer under martallar på hällmark</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,6 +786,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -796,7 +797,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Hällmarksskog.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -814,10 +815,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122924072</v>
+        <v>122924036</v>
       </c>
       <c r="B3" t="n">
-        <v>8441</v>
+        <v>105471</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,32 +831,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -863,14 +863,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öster om Höghäll, Slätthagen, Srm</t>
+          <t>Sydost om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566430</v>
+        <v>566654</v>
       </c>
       <c r="R3" t="n">
-        <v>6584245</v>
+        <v>6584502</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -912,12 +912,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gnagspår på tallåga i hällmark</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,22 +932,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Barrskog. Kontinutietsskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -970,10 +950,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122924036</v>
+        <v>122924806</v>
       </c>
       <c r="B4" t="n">
-        <v>105471</v>
+        <v>56688</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -986,31 +966,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1018,14 +998,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sydost om Höghäll, Slätthagen, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566654</v>
+        <v>566416</v>
       </c>
       <c r="R4" t="n">
-        <v>6584502</v>
+        <v>6584024</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1057,7 +1037,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1067,7 +1047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1076,7 +1056,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1087,7 +1066,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrskog. Kontinutietsskog</t>
+          <t>Hällmarksskog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1105,7 +1084,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122924806</v>
+        <v>122925010</v>
       </c>
       <c r="B5" t="n">
         <v>56688</v>
@@ -1143,7 +1122,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1157,10 +1136,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566416</v>
+        <v>566430</v>
       </c>
       <c r="R5" t="n">
-        <v>6584024</v>
+        <v>6584038</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1205,6 +1184,11 @@
           <t>12:30</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spillning i äldre hällmarksskog. Skogen är avverkningsanmäld.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1221,7 +1205,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Hällmarksskog.</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1239,10 +1223,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122925010</v>
+        <v>122924063</v>
       </c>
       <c r="B6" t="n">
-        <v>56688</v>
+        <v>57494</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1251,25 +1235,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1277,7 +1261,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1287,14 +1271,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566430</v>
+        <v>566588</v>
       </c>
       <c r="R6" t="n">
-        <v>6584038</v>
+        <v>6584418</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1326,7 +1310,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1336,12 +1320,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spillning i äldre hällmarksskog. Skogen är avverkningsanmäld.</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1360,7 +1339,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Äldre barrskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1378,10 +1357,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122924069</v>
+        <v>122924906</v>
       </c>
       <c r="B7" t="n">
-        <v>95136</v>
+        <v>56688</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1394,46 +1373,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öster om Höghäll, Slätthagen, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566445</v>
+        <v>566411</v>
       </c>
       <c r="R7" t="n">
-        <v>6584241</v>
+        <v>6584027</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1465,7 +1444,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1475,12 +1454,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Växer under martallar på hällmark</t>
+          <t>spillning i äldre hälimarksskog. Skogen är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1489,7 +1468,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1500,7 +1478,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Hällmarksskog.</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1518,10 +1496,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122924063</v>
+        <v>122924072</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1530,33 +1508,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1570,10 +1549,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566588</v>
+        <v>566430</v>
       </c>
       <c r="R8" t="n">
-        <v>6584418</v>
+        <v>6584245</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1618,12 +1597,18 @@
           <t>14:00</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gnagspår på tallåga i hällmark</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1634,7 +1619,22 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre barrskog.</t>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1652,7 +1652,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123007993</v>
+        <v>123008173</v>
       </c>
       <c r="B9" t="n">
         <v>8441</v>
@@ -1694,21 +1694,17 @@
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Slätthagen, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566400</v>
+        <v>566354</v>
       </c>
       <c r="R9" t="n">
-        <v>6584187</v>
+        <v>6584152</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1950,10 +1946,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123003959</v>
+        <v>123008919</v>
       </c>
       <c r="B11" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1962,53 +1958,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566582</v>
+        <v>566404</v>
       </c>
       <c r="R11" t="n">
-        <v>6584418</v>
+        <v>6584083</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2032,12 +2025,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2046,28 +2049,54 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123008919</v>
+        <v>123008304</v>
       </c>
       <c r="B12" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2076,47 +2105,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566404</v>
+        <v>566374</v>
       </c>
       <c r="R12" t="n">
-        <v>6584083</v>
+        <v>6584013</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2161,13 +2193,17 @@
           <t>13:00</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på stående död tall.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2179,21 +2215,6 @@
       <c r="AI12" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2211,10 +2232,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123009266</v>
+        <v>123011004</v>
       </c>
       <c r="B13" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2223,34 +2244,33 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2260,14 +2280,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Lövlunda, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566408</v>
+        <v>566010</v>
       </c>
       <c r="R13" t="n">
-        <v>6584004</v>
+        <v>6583585</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2299,7 +2319,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2309,7 +2329,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2318,7 +2338,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2329,22 +2348,22 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Hälmarksskog</t>
+          <t>Äldre barrskogsmiljö</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2362,10 +2381,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123011004</v>
+        <v>123009148</v>
       </c>
       <c r="B14" t="n">
-        <v>57494</v>
+        <v>79384</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2378,46 +2397,41 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lövlunda, Lövlunda, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566010</v>
+        <v>566372</v>
       </c>
       <c r="R14" t="n">
-        <v>6583585</v>
+        <v>6584091</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2449,7 +2463,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2459,7 +2473,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Substrat är gammal tallstubbe i hällmark.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2468,6 +2487,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2478,22 +2498,22 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Äldre barrskogsmiljö</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2511,10 +2531,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123009148</v>
+        <v>123003959</v>
       </c>
       <c r="B15" t="n">
-        <v>79384</v>
+        <v>57494</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2527,44 +2547,49 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566372</v>
+        <v>566582</v>
       </c>
       <c r="R15" t="n">
-        <v>6584091</v>
+        <v>6584418</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2588,27 +2613,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Substrat är gammal tallstubbe i hällmark.</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2617,54 +2627,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123008304</v>
+        <v>123008823</v>
       </c>
       <c r="B16" t="n">
-        <v>57494</v>
+        <v>5173</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2673,33 +2657,34 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2713,10 +2698,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566374</v>
+        <v>566444</v>
       </c>
       <c r="R16" t="n">
-        <v>6584013</v>
+        <v>6583992</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2761,17 +2746,13 @@
           <t>13:00</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska hackmärken på stående död tall.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2783,6 +2764,21 @@
       <c r="AI16" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2800,7 +2796,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123008173</v>
+        <v>123007993</v>
       </c>
       <c r="B17" t="n">
         <v>8441</v>
@@ -2842,17 +2838,21 @@
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Söder om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566354</v>
+        <v>566400</v>
       </c>
       <c r="R17" t="n">
-        <v>6584152</v>
+        <v>6584187</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2947,10 +2947,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123008823</v>
+        <v>123009266</v>
       </c>
       <c r="B18" t="n">
-        <v>5173</v>
+        <v>8441</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2963,21 +2963,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2986,7 +2986,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566444</v>
+        <v>566408</v>
       </c>
       <c r="R18" t="n">
-        <v>6583992</v>
+        <v>6584004</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3065,22 +3065,22 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Hälmarksskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3222,10 +3222,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123034725</v>
+        <v>123003070</v>
       </c>
       <c r="B20" t="n">
-        <v>5173</v>
+        <v>56688</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3238,46 +3238,45 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Farfars trappa, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566550</v>
+        <v>566462</v>
       </c>
       <c r="R20" t="n">
-        <v>6584397</v>
+        <v>6584262</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3304,18 +3303,27 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3327,14 +3335,14 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Anja Hynynen, Emelie Bergermark</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123033899</v>
+        <v>123034725</v>
       </c>
       <c r="B21" t="n">
         <v>5173</v>
@@ -3379,14 +3387,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Farfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566802</v>
+        <v>566550</v>
       </c>
       <c r="R21" t="n">
-        <v>6584534</v>
+        <v>6584397</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3446,10 +3454,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123003070</v>
+        <v>123033899</v>
       </c>
       <c r="B22" t="n">
-        <v>56688</v>
+        <v>5173</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3462,45 +3470,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Morfars trappa, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566462</v>
+        <v>566802</v>
       </c>
       <c r="R22" t="n">
-        <v>6584262</v>
+        <v>6584534</v>
       </c>
       <c r="S22" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3527,27 +3536,18 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anja Hynynen, Emelie Bergermark</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3673,7 +3673,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123077638</v>
+        <v>123080901</v>
       </c>
       <c r="B24" t="n">
         <v>98365</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3716,19 +3716,27 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566640</v>
+        <v>566636</v>
       </c>
       <c r="R24" t="n">
-        <v>6584477</v>
+        <v>6584458</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3775,7 +3783,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Växer längs den gamla kyrkstigen i äldre barrskog.</t>
+          <t>Knärot i äldre barrskog med vinterståndare.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3795,7 +3803,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Äldre barrskogsmiljö</t>
+          <t>Äldre barrskog. Kontinuitetsskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3813,7 +3821,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123080289</v>
+        <v>123077638</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3846,8 +3854,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3857,10 +3873,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566632</v>
+        <v>566640</v>
       </c>
       <c r="R25" t="n">
-        <v>6584457</v>
+        <v>6584477</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3892,7 +3908,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3902,7 +3918,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Växer längs den gamla kyrkstigen i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3922,7 +3943,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Äldre barrskog.</t>
+          <t>Äldre barrskogsmiljö</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3940,7 +3961,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123080901</v>
+        <v>123079585</v>
       </c>
       <c r="B26" t="n">
         <v>98365</v>
@@ -3975,7 +3996,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3983,30 +4004,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566636</v>
+        <v>566632</v>
       </c>
       <c r="R26" t="n">
-        <v>6584458</v>
+        <v>6584462</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4035,7 +4048,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4045,12 +4058,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Knärot i äldre barrskog med vinterståndare.</t>
+          <t>Växer i mossrik äldre barrskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4070,7 +4083,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Äldre barrskog. Kontinuitetsskog</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4088,7 +4101,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123079585</v>
+        <v>123080289</v>
       </c>
       <c r="B27" t="n">
         <v>98365</v>
@@ -4121,16 +4134,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -4143,10 +4148,10 @@
         <v>566632</v>
       </c>
       <c r="R27" t="n">
-        <v>6584462</v>
+        <v>6584457</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4186,11 +4191,6 @@
       <c r="AB27" t="inlineStr">
         <is>
           <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Växer i mossrik äldre barrskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskog.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123232797</v>
+        <v>123241264</v>
       </c>
       <c r="B28" t="n">
-        <v>8430</v>
+        <v>57494</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4240,34 +4240,33 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4277,10 +4276,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566699</v>
+        <v>566553</v>
       </c>
       <c r="R28" t="n">
-        <v>6584476</v>
+        <v>6584351</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4310,28 +4309,17 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4350,10 +4338,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123241264</v>
+        <v>123232797</v>
       </c>
       <c r="B29" t="n">
-        <v>57494</v>
+        <v>8430</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4362,33 +4350,34 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4398,10 +4387,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566553</v>
+        <v>566699</v>
       </c>
       <c r="R29" t="n">
-        <v>6584351</v>
+        <v>6584476</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4431,17 +4420,28 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4460,7 +4460,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123231344</v>
+        <v>123185939</v>
       </c>
       <c r="B30" t="n">
         <v>8441</v>
@@ -4493,7 +4493,11 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -4505,17 +4509,17 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566775</v>
+        <v>566060</v>
       </c>
       <c r="R30" t="n">
-        <v>6584532</v>
+        <v>6583553</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4539,22 +4543,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4563,26 +4567,25 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123185939</v>
+        <v>123231344</v>
       </c>
       <c r="B31" t="n">
         <v>8441</v>
@@ -4615,11 +4618,7 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -4631,17 +4630,17 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lövlunda, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566060</v>
+        <v>566775</v>
       </c>
       <c r="R31" t="n">
-        <v>6583553</v>
+        <v>6584532</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4665,22 +4664,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4689,18 +4688,19 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122924069</v>
+        <v>122924063</v>
       </c>
       <c r="B2" t="n">
-        <v>95136</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566445</v>
+        <v>566588</v>
       </c>
       <c r="R2" t="n">
-        <v>6584241</v>
+        <v>6584418</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -775,18 +775,12 @@
           <t>14:00</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Växer under martallar på hällmark</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -797,7 +791,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Hällmarksskog.</t>
+          <t>Äldre barrskog.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -815,10 +809,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122924036</v>
+        <v>122924069</v>
       </c>
       <c r="B3" t="n">
-        <v>105471</v>
+        <v>95136</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,46 +825,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sydost om Höghäll, Slätthagen, Srm</t>
+          <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566654</v>
+        <v>566445</v>
       </c>
       <c r="R3" t="n">
-        <v>6584502</v>
+        <v>6584241</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -902,7 +896,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -912,7 +906,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Växer under martallar på hällmark</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -932,7 +931,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrskog. Kontinutietsskog</t>
+          <t>Hällmarksskog.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -950,7 +949,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122924806</v>
+        <v>122925010</v>
       </c>
       <c r="B4" t="n">
         <v>56688</v>
@@ -988,7 +987,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1002,10 +1001,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566416</v>
+        <v>566430</v>
       </c>
       <c r="R4" t="n">
-        <v>6584024</v>
+        <v>6584038</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1050,6 +1049,11 @@
           <t>12:30</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spillning i äldre hällmarksskog. Skogen är avverkningsanmäld.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1066,7 +1070,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Hällmarksskog.</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1084,10 +1088,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122925010</v>
+        <v>122924072</v>
       </c>
       <c r="B5" t="n">
-        <v>56688</v>
+        <v>8441</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1100,29 +1104,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1132,14 +1137,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>566430</v>
       </c>
       <c r="R5" t="n">
-        <v>6584038</v>
+        <v>6584245</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1171,7 +1176,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1181,12 +1186,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spillning i äldre hällmarksskog. Skogen är avverkningsanmäld.</t>
+          <t>Gnagspår på tallåga i hällmark</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,6 +1200,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1206,6 +1212,21 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1223,10 +1244,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122924063</v>
+        <v>122924036</v>
       </c>
       <c r="B6" t="n">
-        <v>57494</v>
+        <v>105471</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1235,35 +1256,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1271,14 +1292,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öster om Höghäll, Slätthagen, Srm</t>
+          <t>Sydost om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566588</v>
+        <v>566654</v>
       </c>
       <c r="R6" t="n">
-        <v>6584418</v>
+        <v>6584502</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1310,7 +1331,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1320,7 +1341,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1329,6 +1350,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1339,7 +1361,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre barrskog.</t>
+          <t>Barrskog. Kontinutietsskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1357,7 +1379,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122924906</v>
+        <v>122924806</v>
       </c>
       <c r="B7" t="n">
         <v>56688</v>
@@ -1409,10 +1431,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566411</v>
+        <v>566416</v>
       </c>
       <c r="R7" t="n">
-        <v>6584027</v>
+        <v>6584024</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1457,11 +1479,6 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>spillning i äldre hälimarksskog. Skogen är avverkningsanmäld.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1478,7 +1495,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Hällmarksskog.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1496,10 +1513,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122924072</v>
+        <v>122924906</v>
       </c>
       <c r="B8" t="n">
-        <v>8441</v>
+        <v>56688</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1512,30 +1529,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1545,14 +1561,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Öster om Höghäll, Slätthagen, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566430</v>
+        <v>566411</v>
       </c>
       <c r="R8" t="n">
-        <v>6584245</v>
+        <v>6584027</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1584,7 +1600,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1594,12 +1610,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gnagspår på tallåga i hällmark</t>
+          <t>spillning i äldre hälimarksskog. Skogen är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1608,7 +1624,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1620,21 +1635,6 @@
       <c r="AI8" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1799,10 +1799,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123010595</v>
+        <v>123008304</v>
       </c>
       <c r="B10" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1811,47 +1811,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lövlunda, Lövlunda, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566008</v>
+        <v>566374</v>
       </c>
       <c r="R10" t="n">
-        <v>6583487</v>
+        <v>6584013</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1883,7 +1886,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1893,7 +1896,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på stående död tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1902,7 +1910,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1914,21 +1921,6 @@
       <c r="AI10" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1946,7 +1938,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123008919</v>
+        <v>123007993</v>
       </c>
       <c r="B11" t="n">
         <v>8441</v>
@@ -1988,17 +1980,21 @@
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Söder om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566404</v>
+        <v>566400</v>
       </c>
       <c r="R11" t="n">
-        <v>6584083</v>
+        <v>6584187</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2030,7 +2026,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2040,7 +2036,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2093,10 +2089,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123008304</v>
+        <v>123009148</v>
       </c>
       <c r="B12" t="n">
-        <v>57494</v>
+        <v>79384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2109,46 +2105,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566374</v>
+        <v>566372</v>
       </c>
       <c r="R12" t="n">
-        <v>6584013</v>
+        <v>6584091</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2195,7 +2186,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska hackmärken på stående död tall.</t>
+          <t>Substrat är gammal tallstubbe i hällmark.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2204,6 +2195,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2215,6 +2207,21 @@
       <c r="AI12" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2232,7 +2239,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123011004</v>
+        <v>123003959</v>
       </c>
       <c r="B13" t="n">
         <v>57494</v>
@@ -2265,7 +2272,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
@@ -2273,24 +2284,20 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lövlunda, Lövlunda, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566010</v>
+        <v>566582</v>
       </c>
       <c r="R13" t="n">
-        <v>6583585</v>
+        <v>6584418</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2314,22 +2321,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2340,51 +2337,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Äldre barrskogsmiljö</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123009148</v>
+        <v>123010595</v>
       </c>
       <c r="B14" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2393,45 +2365,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Lövlunda, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566372</v>
+        <v>566008</v>
       </c>
       <c r="R14" t="n">
-        <v>6584091</v>
+        <v>6583487</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2463,7 +2437,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2473,12 +2447,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Substrat är gammal tallstubbe i hällmark.</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2531,10 +2500,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123003959</v>
+        <v>123008823</v>
       </c>
       <c r="B15" t="n">
-        <v>57494</v>
+        <v>5173</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2543,53 +2512,54 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566582</v>
+        <v>566444</v>
       </c>
       <c r="R15" t="n">
-        <v>6584418</v>
+        <v>6583992</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2613,12 +2583,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2627,28 +2607,54 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123008823</v>
+        <v>123008919</v>
       </c>
       <c r="B16" t="n">
-        <v>5173</v>
+        <v>8441</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2661,21 +2667,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2684,24 +2690,20 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566444</v>
+        <v>566404</v>
       </c>
       <c r="R16" t="n">
-        <v>6583992</v>
+        <v>6584083</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2768,17 +2770,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2796,7 +2798,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123007993</v>
+        <v>123009266</v>
       </c>
       <c r="B17" t="n">
         <v>8441</v>
@@ -2845,14 +2847,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Slätthagen, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566400</v>
+        <v>566408</v>
       </c>
       <c r="R17" t="n">
-        <v>6584187</v>
+        <v>6584004</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2884,7 +2886,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2894,7 +2896,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2914,7 +2916,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Hälmarksskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2947,10 +2949,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123009266</v>
+        <v>123011004</v>
       </c>
       <c r="B18" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2959,34 +2961,33 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2996,14 +2997,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Lövlunda, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566408</v>
+        <v>566010</v>
       </c>
       <c r="R18" t="n">
-        <v>6584004</v>
+        <v>6583585</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3035,7 +3036,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3045,7 +3046,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3054,7 +3055,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -3065,22 +3065,22 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Hälmarksskog</t>
+          <t>Äldre barrskogsmiljö</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3098,10 +3098,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123050079</v>
+        <v>123033899</v>
       </c>
       <c r="B19" t="n">
-        <v>98365</v>
+        <v>5173</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3110,39 +3110,36 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3150,13 +3147,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566634</v>
+        <v>566802</v>
       </c>
       <c r="R19" t="n">
-        <v>6584453</v>
+        <v>6584534</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3180,22 +3177,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3204,18 +3191,19 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3342,10 +3330,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123034725</v>
+        <v>123033108</v>
       </c>
       <c r="B21" t="n">
-        <v>5173</v>
+        <v>97319</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3358,43 +3346,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Farfars trappa, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566550</v>
+        <v>566666</v>
       </c>
       <c r="R21" t="n">
-        <v>6584397</v>
+        <v>6584456</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3447,17 +3430,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Anja Hynynen, Emelie Bergermark</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123033899</v>
+        <v>123050079</v>
       </c>
       <c r="B22" t="n">
-        <v>5173</v>
+        <v>98365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3466,36 +3449,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3503,13 +3489,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566802</v>
+        <v>566634</v>
       </c>
       <c r="R22" t="n">
-        <v>6584534</v>
+        <v>6584453</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3533,12 +3519,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3547,29 +3543,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123033108</v>
+        <v>123034725</v>
       </c>
       <c r="B23" t="n">
-        <v>97319</v>
+        <v>5173</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3582,38 +3577,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Farfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566666</v>
+        <v>566550</v>
       </c>
       <c r="R23" t="n">
-        <v>6584456</v>
+        <v>6584397</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3666,14 +3666,14 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anja Hynynen, Emelie Bergermark</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123080901</v>
+        <v>123079585</v>
       </c>
       <c r="B24" t="n">
         <v>98365</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3716,30 +3716,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566636</v>
+        <v>566632</v>
       </c>
       <c r="R24" t="n">
-        <v>6584458</v>
+        <v>6584462</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3768,7 +3760,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3778,12 +3770,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Knärot i äldre barrskog med vinterståndare.</t>
+          <t>Växer i mossrik äldre barrskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3803,7 +3795,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Äldre barrskog. Kontinuitetsskog</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3821,7 +3813,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123077638</v>
+        <v>123080289</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3854,16 +3846,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3873,10 +3857,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566640</v>
+        <v>566632</v>
       </c>
       <c r="R25" t="n">
-        <v>6584477</v>
+        <v>6584457</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3908,7 +3892,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3918,12 +3902,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Växer längs den gamla kyrkstigen i äldre barrskog.</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3943,7 +3922,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Äldre barrskogsmiljö</t>
+          <t>Äldre barrskog.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3961,7 +3940,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123079585</v>
+        <v>123080901</v>
       </c>
       <c r="B26" t="n">
         <v>98365</v>
@@ -3996,7 +3975,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4004,22 +3983,30 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566632</v>
+        <v>566636</v>
       </c>
       <c r="R26" t="n">
-        <v>6584462</v>
+        <v>6584458</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4048,7 +4035,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4058,12 +4045,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Växer i mossrik äldre barrskog.</t>
+          <t>Knärot i äldre barrskog med vinterståndare.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4083,7 +4070,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskog. Kontinuitetsskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4101,7 +4088,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123080289</v>
+        <v>123077638</v>
       </c>
       <c r="B27" t="n">
         <v>98365</v>
@@ -4134,8 +4121,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -4145,10 +4140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566632</v>
+        <v>566640</v>
       </c>
       <c r="R27" t="n">
-        <v>6584457</v>
+        <v>6584477</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4180,7 +4175,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4190,7 +4185,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Växer längs den gamla kyrkstigen i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Äldre barrskog.</t>
+          <t>Äldre barrskogsmiljö</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123241264</v>
+        <v>123232797</v>
       </c>
       <c r="B28" t="n">
-        <v>57494</v>
+        <v>8430</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4240,33 +4240,34 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4276,10 +4277,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566553</v>
+        <v>566699</v>
       </c>
       <c r="R28" t="n">
-        <v>6584351</v>
+        <v>6584476</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4309,17 +4310,28 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4338,10 +4350,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123232797</v>
+        <v>123231344</v>
       </c>
       <c r="B29" t="n">
-        <v>8430</v>
+        <v>8441</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4354,21 +4366,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4387,10 +4399,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566699</v>
+        <v>566775</v>
       </c>
       <c r="R29" t="n">
-        <v>6584476</v>
+        <v>6584532</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4422,7 +4434,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4432,7 +4444,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4585,10 +4597,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123231344</v>
+        <v>123241264</v>
       </c>
       <c r="B31" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4597,34 +4609,33 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4634,10 +4645,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566775</v>
+        <v>566553</v>
       </c>
       <c r="R31" t="n">
-        <v>6584532</v>
+        <v>6584351</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4667,28 +4678,17 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4707,10 +4707,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123271947</v>
+        <v>123236226</v>
       </c>
       <c r="B32" t="n">
-        <v>90952</v>
+        <v>90917</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4719,25 +4719,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4783,9 +4783,19 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4813,10 +4823,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123236226</v>
+        <v>123271947</v>
       </c>
       <c r="B33" t="n">
-        <v>90917</v>
+        <v>90952</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4825,25 +4835,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4889,19 +4899,9 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>16:52</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>16:52</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -2353,10 +2353,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123010595</v>
+        <v>123008823</v>
       </c>
       <c r="B14" t="n">
-        <v>8441</v>
+        <v>5173</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2369,21 +2369,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2392,20 +2392,24 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lövlunda, Lövlunda, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566008</v>
+        <v>566444</v>
       </c>
       <c r="R14" t="n">
-        <v>6583487</v>
+        <v>6583992</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2437,7 +2441,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2447,7 +2451,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2472,17 +2476,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2500,10 +2504,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123008823</v>
+        <v>123010595</v>
       </c>
       <c r="B15" t="n">
-        <v>5173</v>
+        <v>8441</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2516,21 +2520,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2539,24 +2543,20 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Lövlunda, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566444</v>
+        <v>566008</v>
       </c>
       <c r="R15" t="n">
-        <v>6583992</v>
+        <v>6583487</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2623,17 +2623,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122924063</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -809,10 +809,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122924069</v>
+        <v>122925010</v>
       </c>
       <c r="B3" t="n">
-        <v>95136</v>
+        <v>56691</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,46 +825,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öster om Höghäll, Slätthagen, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566445</v>
+        <v>566430</v>
       </c>
       <c r="R3" t="n">
-        <v>6584241</v>
+        <v>6584038</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -896,7 +896,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Växer under martallar på hällmark</t>
+          <t>Spillning i äldre hällmarksskog. Skogen är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,7 +920,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -931,7 +930,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Hällmarksskog.</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -949,10 +948,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122925010</v>
+        <v>122924906</v>
       </c>
       <c r="B4" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -987,7 +986,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1001,10 +1000,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566430</v>
+        <v>566411</v>
       </c>
       <c r="R4" t="n">
-        <v>6584038</v>
+        <v>6584027</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1051,7 +1050,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spillning i äldre hällmarksskog. Skogen är avverkningsanmäld.</t>
+          <t>spillning i äldre hälimarksskog. Skogen är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1088,10 +1087,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122924072</v>
+        <v>122924069</v>
       </c>
       <c r="B5" t="n">
-        <v>8441</v>
+        <v>95139</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1104,47 +1103,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566430</v>
+        <v>566445</v>
       </c>
       <c r="R5" t="n">
-        <v>6584245</v>
+        <v>6584241</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1191,7 +1189,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gnagspår på tallåga i hällmark</t>
+          <t>Växer under martallar på hällmark</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1211,22 +1209,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Hällmarksskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1247,7 +1230,7 @@
         <v>122924036</v>
       </c>
       <c r="B6" t="n">
-        <v>105471</v>
+        <v>105474</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1382,7 +1365,7 @@
         <v>122924806</v>
       </c>
       <c r="B7" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1513,10 +1496,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122924906</v>
+        <v>122924072</v>
       </c>
       <c r="B8" t="n">
-        <v>56688</v>
+        <v>8441</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1529,29 +1512,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1561,14 +1545,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566411</v>
+        <v>566430</v>
       </c>
       <c r="R8" t="n">
-        <v>6584027</v>
+        <v>6584245</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1600,7 +1584,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1610,12 +1594,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>spillning i äldre hälimarksskog. Skogen är avverkningsanmäld.</t>
+          <t>Gnagspår på tallåga i hällmark</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1624,6 +1608,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1635,6 +1620,21 @@
       <c r="AI8" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1799,10 +1799,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123008304</v>
+        <v>123009266</v>
       </c>
       <c r="B10" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1811,33 +1811,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1851,10 +1852,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566374</v>
+        <v>566408</v>
       </c>
       <c r="R10" t="n">
-        <v>6584013</v>
+        <v>6584004</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1899,17 +1900,13 @@
           <t>13:00</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska hackmärken på stående död tall.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1920,7 +1917,22 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Hälmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1938,10 +1950,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123007993</v>
+        <v>123008823</v>
       </c>
       <c r="B11" t="n">
-        <v>8441</v>
+        <v>5173</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1954,21 +1966,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1977,7 +1989,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1987,14 +1999,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Slätthagen, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566400</v>
+        <v>566444</v>
       </c>
       <c r="R11" t="n">
-        <v>6584187</v>
+        <v>6583992</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2026,7 +2038,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2036,7 +2048,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2061,17 +2073,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2092,7 +2104,7 @@
         <v>123009148</v>
       </c>
       <c r="B12" t="n">
-        <v>79384</v>
+        <v>79387</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2239,10 +2251,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123003959</v>
+        <v>123008919</v>
       </c>
       <c r="B13" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2251,53 +2263,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566582</v>
+        <v>566404</v>
       </c>
       <c r="R13" t="n">
-        <v>6584418</v>
+        <v>6584083</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2321,12 +2330,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2335,28 +2354,54 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123008823</v>
+        <v>123007993</v>
       </c>
       <c r="B14" t="n">
-        <v>5173</v>
+        <v>8441</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2369,21 +2414,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2392,7 +2437,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2402,14 +2447,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Söder om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566444</v>
+        <v>566400</v>
       </c>
       <c r="R14" t="n">
-        <v>6583992</v>
+        <v>6584187</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2441,7 +2486,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2451,7 +2496,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2476,17 +2521,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2651,10 +2696,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123008919</v>
+        <v>123011004</v>
       </c>
       <c r="B16" t="n">
-        <v>8441</v>
+        <v>57497</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2663,47 +2708,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Lövlunda, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566404</v>
+        <v>566010</v>
       </c>
       <c r="R16" t="n">
-        <v>6584083</v>
+        <v>6583585</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2735,7 +2783,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2745,7 +2793,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2754,7 +2802,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2765,22 +2812,22 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Äldre barrskogsmiljö</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2798,10 +2845,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123009266</v>
+        <v>123008304</v>
       </c>
       <c r="B17" t="n">
-        <v>8441</v>
+        <v>57497</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2810,34 +2857,33 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2851,10 +2897,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566408</v>
+        <v>566374</v>
       </c>
       <c r="R17" t="n">
-        <v>6584004</v>
+        <v>6584013</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2899,13 +2945,17 @@
           <t>13:00</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på stående död tall.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2916,22 +2966,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Hälmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2949,10 +2984,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123011004</v>
+        <v>123003959</v>
       </c>
       <c r="B18" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2982,7 +3017,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
@@ -2990,24 +3029,20 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lövlunda, Lövlunda, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566010</v>
+        <v>566582</v>
       </c>
       <c r="R18" t="n">
-        <v>6583585</v>
+        <v>6584418</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3031,22 +3066,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3057,48 +3082,23 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Äldre barrskogsmiljö</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123033899</v>
+        <v>123034725</v>
       </c>
       <c r="B19" t="n">
         <v>5173</v>
@@ -3143,14 +3143,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Farfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566802</v>
+        <v>566550</v>
       </c>
       <c r="R19" t="n">
-        <v>6584534</v>
+        <v>6584397</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3210,10 +3210,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123003070</v>
+        <v>123050079</v>
       </c>
       <c r="B20" t="n">
-        <v>56688</v>
+        <v>98368</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3222,49 +3222,53 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Morfars trappa, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566462</v>
+        <v>566634</v>
       </c>
       <c r="R20" t="n">
-        <v>6584262</v>
+        <v>6584453</v>
       </c>
       <c r="S20" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3288,22 +3292,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3318,22 +3322,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anja Hynynen, Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123033108</v>
+        <v>123033899</v>
       </c>
       <c r="B21" t="n">
-        <v>97319</v>
+        <v>5173</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3346,27 +3350,32 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3374,10 +3383,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566666</v>
+        <v>566802</v>
       </c>
       <c r="R21" t="n">
-        <v>6584456</v>
+        <v>6584534</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3430,17 +3439,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anja Hynynen, Emelie Bergermark</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123050079</v>
+        <v>123033108</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>97322</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3449,37 +3458,29 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -3489,13 +3490,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566634</v>
+        <v>566666</v>
       </c>
       <c r="R22" t="n">
-        <v>6584453</v>
+        <v>6584456</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3519,22 +3520,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3543,28 +3534,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen, Emelie Bergermark</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123034725</v>
+        <v>123003070</v>
       </c>
       <c r="B23" t="n">
-        <v>5173</v>
+        <v>56691</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3577,46 +3569,45 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Farfars trappa, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566550</v>
+        <v>566462</v>
       </c>
       <c r="R23" t="n">
-        <v>6584397</v>
+        <v>6584262</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3643,18 +3634,27 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3666,17 +3666,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Anja Hynynen, Emelie Bergermark</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123079585</v>
+        <v>123077638</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3725,13 +3725,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566632</v>
+        <v>566640</v>
       </c>
       <c r="R24" t="n">
-        <v>6584462</v>
+        <v>6584477</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Växer i mossrik äldre barrskog.</t>
+          <t>Växer längs den gamla kyrkstigen i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskogsmiljö</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3816,7 +3816,7 @@
         <v>123080289</v>
       </c>
       <c r="B25" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>123080901</v>
       </c>
       <c r="B26" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4088,10 +4088,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123077638</v>
+        <v>123079585</v>
       </c>
       <c r="B27" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4140,13 +4140,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566640</v>
+        <v>566632</v>
       </c>
       <c r="R27" t="n">
-        <v>6584477</v>
+        <v>6584462</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Växer längs den gamla kyrkstigen i äldre barrskog.</t>
+          <t>Växer i mossrik äldre barrskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Äldre barrskogsmiljö</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123232797</v>
+        <v>123231344</v>
       </c>
       <c r="B28" t="n">
-        <v>8430</v>
+        <v>8441</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4244,21 +4244,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566699</v>
+        <v>566775</v>
       </c>
       <c r="R28" t="n">
-        <v>6584476</v>
+        <v>6584532</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4350,7 +4350,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123231344</v>
+        <v>123185939</v>
       </c>
       <c r="B29" t="n">
         <v>8441</v>
@@ -4383,7 +4383,11 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -4395,17 +4399,17 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566775</v>
+        <v>566060</v>
       </c>
       <c r="R29" t="n">
-        <v>6584532</v>
+        <v>6583553</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4429,22 +4433,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4453,29 +4457,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123185939</v>
+        <v>123232797</v>
       </c>
       <c r="B30" t="n">
-        <v>8441</v>
+        <v>8430</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4488,28 +4491,24 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -4521,17 +4520,17 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lövlunda, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566060</v>
+        <v>566699</v>
       </c>
       <c r="R30" t="n">
-        <v>6583553</v>
+        <v>6584476</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4555,22 +4554,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4579,18 +4578,19 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4600,7 +4600,7 @@
         <v>123241264</v>
       </c>
       <c r="B31" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>123236226</v>
       </c>
       <c r="B32" t="n">
-        <v>90917</v>
+        <v>90920</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>123271947</v>
       </c>
       <c r="B33" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -809,7 +809,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122925010</v>
+        <v>122924806</v>
       </c>
       <c r="B3" t="n">
         <v>56691</v>
@@ -847,7 +847,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566430</v>
+        <v>566416</v>
       </c>
       <c r="R3" t="n">
-        <v>6584038</v>
+        <v>6584024</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -909,11 +909,6 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spillning i äldre hällmarksskog. Skogen är avverkningsanmäld.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -930,7 +925,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Hällmarksskog.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -948,10 +943,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122924906</v>
+        <v>122924036</v>
       </c>
       <c r="B4" t="n">
-        <v>56691</v>
+        <v>105476</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -964,31 +959,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -996,14 +991,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Sydost om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566411</v>
+        <v>566654</v>
       </c>
       <c r="R4" t="n">
-        <v>6584027</v>
+        <v>6584502</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1035,7 +1030,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1045,12 +1040,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>spillning i äldre hälimarksskog. Skogen är avverkningsanmäld.</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,6 +1049,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1069,7 +1060,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Barrskog. Kontinutietsskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1087,10 +1078,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122924069</v>
+        <v>122925010</v>
       </c>
       <c r="B5" t="n">
-        <v>95139</v>
+        <v>56691</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1103,46 +1094,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öster om Höghäll, Slätthagen, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566445</v>
+        <v>566430</v>
       </c>
       <c r="R5" t="n">
-        <v>6584241</v>
+        <v>6584038</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1174,7 +1165,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1184,12 +1175,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växer under martallar på hällmark</t>
+          <t>Spillning i äldre hällmarksskog. Skogen är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1198,7 +1189,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1209,7 +1199,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Hällmarksskog.</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1227,10 +1217,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122924036</v>
+        <v>122924069</v>
       </c>
       <c r="B6" t="n">
-        <v>105474</v>
+        <v>95141</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1243,46 +1233,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sydost om Höghäll, Slätthagen, Srm</t>
+          <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566654</v>
+        <v>566445</v>
       </c>
       <c r="R6" t="n">
-        <v>6584502</v>
+        <v>6584241</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1314,7 +1304,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1324,7 +1314,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Växer under martallar på hällmark</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1344,7 +1339,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrskog. Kontinutietsskog</t>
+          <t>Hällmarksskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1362,10 +1357,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122924806</v>
+        <v>122924072</v>
       </c>
       <c r="B7" t="n">
-        <v>56691</v>
+        <v>8441</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1378,29 +1373,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1410,14 +1406,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566416</v>
+        <v>566430</v>
       </c>
       <c r="R7" t="n">
-        <v>6584024</v>
+        <v>6584245</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1449,7 +1445,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1459,7 +1455,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gnagspår på tallåga i hällmark</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1468,6 +1469,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1478,7 +1480,22 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Hällmarksskog.</t>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1496,10 +1513,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122924072</v>
+        <v>122924906</v>
       </c>
       <c r="B8" t="n">
-        <v>8441</v>
+        <v>56691</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1512,30 +1529,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1545,14 +1561,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Öster om Höghäll, Slätthagen, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566430</v>
+        <v>566411</v>
       </c>
       <c r="R8" t="n">
-        <v>6584245</v>
+        <v>6584027</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1584,7 +1600,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1594,12 +1610,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gnagspår på tallåga i hällmark</t>
+          <t>spillning i äldre hälimarksskog. Skogen är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1608,7 +1624,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1620,21 +1635,6 @@
       <c r="AI8" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1652,7 +1652,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123008173</v>
+        <v>123010595</v>
       </c>
       <c r="B9" t="n">
         <v>8441</v>
@@ -1697,14 +1697,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Lövlunda, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566354</v>
+        <v>566008</v>
       </c>
       <c r="R9" t="n">
-        <v>6584152</v>
+        <v>6583487</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1799,7 +1799,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123009266</v>
+        <v>123008173</v>
       </c>
       <c r="B10" t="n">
         <v>8441</v>
@@ -1841,21 +1841,17 @@
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566408</v>
+        <v>566354</v>
       </c>
       <c r="R10" t="n">
-        <v>6584004</v>
+        <v>6584152</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1887,7 +1883,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1897,7 +1893,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1917,7 +1913,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Hälmarksskog</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1950,10 +1946,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123008823</v>
+        <v>123008919</v>
       </c>
       <c r="B11" t="n">
-        <v>5173</v>
+        <v>8441</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1966,21 +1962,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1989,24 +1985,20 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566444</v>
+        <v>566404</v>
       </c>
       <c r="R11" t="n">
-        <v>6583992</v>
+        <v>6584083</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2073,17 +2065,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2101,10 +2093,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123009148</v>
+        <v>123007993</v>
       </c>
       <c r="B12" t="n">
-        <v>79387</v>
+        <v>8441</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2113,45 +2105,51 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Söder om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566372</v>
+        <v>566400</v>
       </c>
       <c r="R12" t="n">
-        <v>6584091</v>
+        <v>6584187</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2183,7 +2181,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2193,12 +2191,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Substrat är gammal tallstubbe i hällmark.</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2251,10 +2244,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123008919</v>
+        <v>123009148</v>
       </c>
       <c r="B13" t="n">
-        <v>8441</v>
+        <v>79389</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2263,34 +2256,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2300,10 +2291,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566404</v>
+        <v>566372</v>
       </c>
       <c r="R13" t="n">
-        <v>6584083</v>
+        <v>6584091</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2346,6 +2337,11 @@
       <c r="AB13" t="inlineStr">
         <is>
           <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Substrat är gammal tallstubbe i hällmark.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2398,10 +2394,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123007993</v>
+        <v>123008304</v>
       </c>
       <c r="B14" t="n">
-        <v>8441</v>
+        <v>57497</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2410,34 +2406,33 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2447,14 +2442,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Slätthagen, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566400</v>
+        <v>566374</v>
       </c>
       <c r="R14" t="n">
-        <v>6584187</v>
+        <v>6584013</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2486,7 +2481,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2496,7 +2491,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på stående död tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2505,7 +2505,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2517,21 +2516,6 @@
       <c r="AI14" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2549,10 +2533,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123010595</v>
+        <v>123008823</v>
       </c>
       <c r="B15" t="n">
-        <v>8441</v>
+        <v>5173</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2565,21 +2549,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2588,20 +2572,24 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lövlunda, Lövlunda, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566008</v>
+        <v>566444</v>
       </c>
       <c r="R15" t="n">
-        <v>6583487</v>
+        <v>6583992</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2633,7 +2621,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2643,7 +2631,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2668,17 +2656,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2696,10 +2684,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123011004</v>
+        <v>123009266</v>
       </c>
       <c r="B16" t="n">
-        <v>57497</v>
+        <v>8441</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2708,33 +2696,34 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2744,14 +2733,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lövlunda, Lövlunda, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566010</v>
+        <v>566408</v>
       </c>
       <c r="R16" t="n">
-        <v>6583585</v>
+        <v>6584004</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2783,7 +2772,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2793,7 +2782,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2802,6 +2791,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2812,22 +2802,22 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre barrskogsmiljö</t>
+          <t>Hälmarksskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2845,7 +2835,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123008304</v>
+        <v>123003959</v>
       </c>
       <c r="B17" t="n">
         <v>57497</v>
@@ -2878,7 +2868,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
@@ -2886,24 +2880,20 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566374</v>
+        <v>566582</v>
       </c>
       <c r="R17" t="n">
-        <v>6584013</v>
+        <v>6584418</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2927,27 +2917,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska hackmärken på stående död tall.</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2958,33 +2933,23 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Hällmarksskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123003959</v>
+        <v>123011004</v>
       </c>
       <c r="B18" t="n">
         <v>57497</v>
@@ -3017,11 +2982,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
@@ -3029,20 +2990,24 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Lövlunda, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566582</v>
+        <v>566010</v>
       </c>
       <c r="R18" t="n">
-        <v>6584418</v>
+        <v>6583585</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3066,12 +3031,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3082,23 +3057,48 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Äldre barrskogsmiljö</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123034725</v>
+        <v>123033899</v>
       </c>
       <c r="B19" t="n">
         <v>5173</v>
@@ -3143,14 +3143,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Farfars trappa, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566550</v>
+        <v>566802</v>
       </c>
       <c r="R19" t="n">
-        <v>6584397</v>
+        <v>6584534</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3210,10 +3210,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123050079</v>
+        <v>123034725</v>
       </c>
       <c r="B20" t="n">
-        <v>98368</v>
+        <v>5173</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3222,53 +3222,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Farfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566634</v>
+        <v>566550</v>
       </c>
       <c r="R20" t="n">
-        <v>6584453</v>
+        <v>6584397</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3292,22 +3289,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3316,28 +3303,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123033899</v>
+        <v>123033108</v>
       </c>
       <c r="B21" t="n">
-        <v>5173</v>
+        <v>97324</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3350,32 +3338,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3383,10 +3366,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566802</v>
+        <v>566666</v>
       </c>
       <c r="R21" t="n">
-        <v>6584534</v>
+        <v>6584456</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3439,17 +3422,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Anja Hynynen, Emelie Bergermark</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123033108</v>
+        <v>123003070</v>
       </c>
       <c r="B22" t="n">
-        <v>97322</v>
+        <v>56691</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3462,41 +3445,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566666</v>
+        <v>566462</v>
       </c>
       <c r="R22" t="n">
-        <v>6584456</v>
+        <v>6584262</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3523,18 +3510,27 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3553,10 +3549,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123003070</v>
+        <v>123050079</v>
       </c>
       <c r="B23" t="n">
-        <v>56691</v>
+        <v>98370</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3565,49 +3561,53 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Morfars trappa, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566462</v>
+        <v>566634</v>
       </c>
       <c r="R23" t="n">
-        <v>6584262</v>
+        <v>6584453</v>
       </c>
       <c r="S23" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3631,22 +3631,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3661,22 +3661,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anja Hynynen, Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123077638</v>
+        <v>123080901</v>
       </c>
       <c r="B24" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3716,19 +3716,27 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566640</v>
+        <v>566636</v>
       </c>
       <c r="R24" t="n">
-        <v>6584477</v>
+        <v>6584458</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3775,7 +3783,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Växer längs den gamla kyrkstigen i äldre barrskog.</t>
+          <t>Knärot i äldre barrskog med vinterståndare.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3795,7 +3803,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Äldre barrskogsmiljö</t>
+          <t>Äldre barrskog. Kontinuitetsskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3813,10 +3821,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123080289</v>
+        <v>123079585</v>
       </c>
       <c r="B25" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3846,8 +3854,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3860,10 +3876,10 @@
         <v>566632</v>
       </c>
       <c r="R25" t="n">
-        <v>6584457</v>
+        <v>6584462</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3903,6 +3919,11 @@
       <c r="AB25" t="inlineStr">
         <is>
           <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Växer i mossrik äldre barrskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3922,7 +3943,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Äldre barrskog.</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3940,10 +3961,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123080901</v>
+        <v>123077638</v>
       </c>
       <c r="B26" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3975,7 +3996,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3983,27 +4004,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566636</v>
+        <v>566640</v>
       </c>
       <c r="R26" t="n">
-        <v>6584458</v>
+        <v>6584477</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4050,7 +4063,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Knärot i äldre barrskog med vinterståndare.</t>
+          <t>Växer längs den gamla kyrkstigen i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4070,7 +4083,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Äldre barrskog. Kontinuitetsskog</t>
+          <t>Äldre barrskogsmiljö</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4088,10 +4101,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123079585</v>
+        <v>123080289</v>
       </c>
       <c r="B27" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4121,16 +4134,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -4143,10 +4148,10 @@
         <v>566632</v>
       </c>
       <c r="R27" t="n">
-        <v>6584462</v>
+        <v>6584457</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4186,11 +4191,6 @@
       <c r="AB27" t="inlineStr">
         <is>
           <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Växer i mossrik äldre barrskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskog.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4475,10 +4475,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123232797</v>
+        <v>123241264</v>
       </c>
       <c r="B30" t="n">
-        <v>8430</v>
+        <v>57497</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4487,34 +4487,33 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4524,10 +4523,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566699</v>
+        <v>566553</v>
       </c>
       <c r="R30" t="n">
-        <v>6584476</v>
+        <v>6584351</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4557,28 +4556,17 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4597,10 +4585,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123241264</v>
+        <v>123232797</v>
       </c>
       <c r="B31" t="n">
-        <v>57497</v>
+        <v>8430</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4609,33 +4597,34 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4645,10 +4634,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566553</v>
+        <v>566699</v>
       </c>
       <c r="R31" t="n">
-        <v>6584351</v>
+        <v>6584476</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4678,17 +4667,28 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4710,7 +4710,7 @@
         <v>123236226</v>
       </c>
       <c r="B32" t="n">
-        <v>90920</v>
+        <v>90922</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>123271947</v>
       </c>
       <c r="B33" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -943,10 +943,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122924036</v>
+        <v>122925010</v>
       </c>
       <c r="B4" t="n">
-        <v>105476</v>
+        <v>56691</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -959,31 +959,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -991,14 +991,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sydost om Höghäll, Slätthagen, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566654</v>
+        <v>566430</v>
       </c>
       <c r="R4" t="n">
-        <v>6584502</v>
+        <v>6584038</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1040,7 +1040,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spillning i äldre hällmarksskog. Skogen är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,7 +1054,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1060,7 +1064,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrskog. Kontinutietsskog</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1078,10 +1082,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122925010</v>
+        <v>122924069</v>
       </c>
       <c r="B5" t="n">
-        <v>56691</v>
+        <v>95147</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1094,46 +1098,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566430</v>
+        <v>566445</v>
       </c>
       <c r="R5" t="n">
-        <v>6584038</v>
+        <v>6584241</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1165,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1175,12 +1179,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spillning i äldre hällmarksskog. Skogen är avverkningsanmäld.</t>
+          <t>Växer under martallar på hällmark</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1189,6 +1193,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1199,7 +1204,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Hällmarksskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1217,10 +1222,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122924069</v>
+        <v>122924072</v>
       </c>
       <c r="B6" t="n">
-        <v>95141</v>
+        <v>8441</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1233,46 +1238,47 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566445</v>
+        <v>566430</v>
       </c>
       <c r="R6" t="n">
-        <v>6584241</v>
+        <v>6584245</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1319,7 +1325,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Växer under martallar på hällmark</t>
+          <t>Gnagspår på tallåga i hällmark</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1339,7 +1345,22 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Hällmarksskog.</t>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1357,10 +1378,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122924072</v>
+        <v>122924906</v>
       </c>
       <c r="B7" t="n">
-        <v>8441</v>
+        <v>56691</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1373,30 +1394,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1406,14 +1426,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öster om Höghäll, Slätthagen, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566430</v>
+        <v>566411</v>
       </c>
       <c r="R7" t="n">
-        <v>6584245</v>
+        <v>6584027</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1445,7 +1465,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1455,12 +1475,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gnagspår på tallåga i hällmark</t>
+          <t>spillning i äldre hälimarksskog. Skogen är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1469,7 +1489,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1481,21 +1500,6 @@
       <c r="AI7" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1513,10 +1517,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122924906</v>
+        <v>122924036</v>
       </c>
       <c r="B8" t="n">
-        <v>56691</v>
+        <v>105482</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1529,31 +1533,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1561,14 +1565,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Sydost om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566411</v>
+        <v>566654</v>
       </c>
       <c r="R8" t="n">
-        <v>6584027</v>
+        <v>6584502</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1600,7 +1604,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1610,12 +1614,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>spillning i äldre hälimarksskog. Skogen är avverkningsanmäld.</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1624,6 +1623,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Barrskog. Kontinutietsskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1652,7 +1652,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123010595</v>
+        <v>123009266</v>
       </c>
       <c r="B9" t="n">
         <v>8441</v>
@@ -1694,17 +1694,21 @@
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lövlunda, Lövlunda, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566008</v>
+        <v>566408</v>
       </c>
       <c r="R9" t="n">
-        <v>6583487</v>
+        <v>6584004</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1736,7 +1740,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1746,7 +1750,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1766,7 +1770,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Hälmarksskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1799,10 +1803,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123008173</v>
+        <v>123011004</v>
       </c>
       <c r="B10" t="n">
-        <v>8441</v>
+        <v>57497</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1811,47 +1815,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Lövlunda, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566354</v>
+        <v>566010</v>
       </c>
       <c r="R10" t="n">
-        <v>6584152</v>
+        <v>6583585</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1883,7 +1890,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1893,7 +1900,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1902,7 +1909,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1913,22 +1919,22 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Äldre barrskogsmiljö</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1946,10 +1952,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123008919</v>
+        <v>123008304</v>
       </c>
       <c r="B11" t="n">
-        <v>8441</v>
+        <v>57497</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1958,47 +1964,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566404</v>
+        <v>566374</v>
       </c>
       <c r="R11" t="n">
-        <v>6584083</v>
+        <v>6584013</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2043,13 +2052,17 @@
           <t>13:00</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på stående död tall.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2061,21 +2074,6 @@
       <c r="AI11" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2244,10 +2242,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123009148</v>
+        <v>123008173</v>
       </c>
       <c r="B13" t="n">
-        <v>79389</v>
+        <v>8441</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2256,32 +2254,34 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566372</v>
+        <v>566354</v>
       </c>
       <c r="R13" t="n">
-        <v>6584091</v>
+        <v>6584152</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2336,12 +2336,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Substrat är gammal tallstubbe i hällmark.</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2394,10 +2389,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123008304</v>
+        <v>123010595</v>
       </c>
       <c r="B14" t="n">
-        <v>57497</v>
+        <v>8441</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2406,50 +2401,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Lövlunda, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566374</v>
+        <v>566008</v>
       </c>
       <c r="R14" t="n">
-        <v>6584013</v>
+        <v>6583487</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2481,7 +2473,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2491,12 +2483,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska hackmärken på stående död tall.</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2505,6 +2492,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2516,6 +2504,21 @@
       <c r="AI14" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2533,10 +2536,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123008823</v>
+        <v>123009148</v>
       </c>
       <c r="B15" t="n">
-        <v>5173</v>
+        <v>79390</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2545,51 +2548,45 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566444</v>
+        <v>566372</v>
       </c>
       <c r="R15" t="n">
-        <v>6583992</v>
+        <v>6584091</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2634,6 +2631,11 @@
           <t>13:00</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Substrat är gammal tallstubbe i hällmark.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2656,17 +2658,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2684,10 +2686,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123009266</v>
+        <v>123008823</v>
       </c>
       <c r="B16" t="n">
-        <v>8441</v>
+        <v>5173</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2700,21 +2702,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2723,7 +2725,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2737,10 +2739,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566408</v>
+        <v>566444</v>
       </c>
       <c r="R16" t="n">
-        <v>6584004</v>
+        <v>6583992</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2802,22 +2804,22 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Hälmarksskog</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2835,10 +2837,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123003959</v>
+        <v>123008919</v>
       </c>
       <c r="B17" t="n">
-        <v>57497</v>
+        <v>8441</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2847,53 +2849,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566582</v>
+        <v>566404</v>
       </c>
       <c r="R17" t="n">
-        <v>6584418</v>
+        <v>6584083</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2917,12 +2916,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2931,25 +2940,51 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123011004</v>
+        <v>123003959</v>
       </c>
       <c r="B18" t="n">
         <v>57497</v>
@@ -2982,7 +3017,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
@@ -2990,24 +3029,20 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lövlunda, Lövlunda, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566010</v>
+        <v>566582</v>
       </c>
       <c r="R18" t="n">
-        <v>6583585</v>
+        <v>6584418</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3031,22 +3066,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3057,48 +3082,23 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Äldre barrskogsmiljö</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123033899</v>
+        <v>123034725</v>
       </c>
       <c r="B19" t="n">
         <v>5173</v>
@@ -3143,14 +3143,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Farfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566802</v>
+        <v>566550</v>
       </c>
       <c r="R19" t="n">
-        <v>6584534</v>
+        <v>6584397</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3210,7 +3210,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123034725</v>
+        <v>123033899</v>
       </c>
       <c r="B20" t="n">
         <v>5173</v>
@@ -3255,14 +3255,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Farfars trappa, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566550</v>
+        <v>566802</v>
       </c>
       <c r="R20" t="n">
-        <v>6584397</v>
+        <v>6584534</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3322,10 +3322,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123033108</v>
+        <v>123003070</v>
       </c>
       <c r="B21" t="n">
-        <v>97324</v>
+        <v>56691</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3338,41 +3338,45 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566666</v>
+        <v>566462</v>
       </c>
       <c r="R21" t="n">
-        <v>6584456</v>
+        <v>6584262</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3399,18 +3403,27 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3429,10 +3442,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123003070</v>
+        <v>123033108</v>
       </c>
       <c r="B22" t="n">
-        <v>56691</v>
+        <v>97330</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3445,45 +3458,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Morfars trappa, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566462</v>
+        <v>566666</v>
       </c>
       <c r="R22" t="n">
-        <v>6584262</v>
+        <v>6584456</v>
       </c>
       <c r="S22" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3510,27 +3519,18 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3552,7 +3552,7 @@
         <v>123050079</v>
       </c>
       <c r="B23" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>123080901</v>
       </c>
       <c r="B24" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>123079585</v>
       </c>
       <c r="B25" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123077638</v>
+        <v>123080289</v>
       </c>
       <c r="B26" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3994,16 +3994,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -4013,10 +4005,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566640</v>
+        <v>566632</v>
       </c>
       <c r="R26" t="n">
-        <v>6584477</v>
+        <v>6584457</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4048,7 +4040,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4058,12 +4050,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Växer längs den gamla kyrkstigen i äldre barrskog.</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4083,7 +4070,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Äldre barrskogsmiljö</t>
+          <t>Äldre barrskog.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4101,10 +4088,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123080289</v>
+        <v>123077638</v>
       </c>
       <c r="B27" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4134,8 +4121,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -4145,10 +4140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566632</v>
+        <v>566640</v>
       </c>
       <c r="R27" t="n">
-        <v>6584457</v>
+        <v>6584477</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4180,7 +4175,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4190,7 +4185,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Växer längs den gamla kyrkstigen i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Äldre barrskog.</t>
+          <t>Äldre barrskogsmiljö</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4350,10 +4350,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123185939</v>
+        <v>123241264</v>
       </c>
       <c r="B29" t="n">
-        <v>8441</v>
+        <v>57497</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4362,54 +4362,49 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lövlunda, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566060</v>
+        <v>566553</v>
       </c>
       <c r="R29" t="n">
-        <v>6583553</v>
+        <v>6584351</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4433,22 +4428,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:23</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:23</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4463,22 +4448,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123241264</v>
+        <v>123232797</v>
       </c>
       <c r="B30" t="n">
-        <v>57497</v>
+        <v>8430</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4487,33 +4472,34 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4523,10 +4509,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566553</v>
+        <v>566699</v>
       </c>
       <c r="R30" t="n">
-        <v>6584351</v>
+        <v>6584476</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4556,17 +4542,28 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4585,10 +4582,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123232797</v>
+        <v>123185939</v>
       </c>
       <c r="B31" t="n">
-        <v>8430</v>
+        <v>8441</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4601,24 +4598,28 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -4630,17 +4631,17 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566699</v>
+        <v>566060</v>
       </c>
       <c r="R31" t="n">
-        <v>6584476</v>
+        <v>6583553</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4664,22 +4665,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4688,19 +4689,18 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4710,7 +4710,7 @@
         <v>123236226</v>
       </c>
       <c r="B32" t="n">
-        <v>90922</v>
+        <v>90928</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>123271947</v>
       </c>
       <c r="B33" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4927,6 +4927,231 @@
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>123527972</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Morfars trappa, Morfars trappa, Srm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>566423</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6584223</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>123530730</v>
+      </c>
+      <c r="B35" t="n">
+        <v>56691</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Morfars trappa, Morfars trappa, Srm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>566427</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6584117</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -2246,10 +2246,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123008823</v>
+        <v>123008919</v>
       </c>
       <c r="B13" t="n">
-        <v>5173</v>
+        <v>8441</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2262,21 +2262,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2285,24 +2285,20 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566444</v>
+        <v>566404</v>
       </c>
       <c r="R13" t="n">
-        <v>6583992</v>
+        <v>6584083</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2369,17 +2365,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2397,10 +2393,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123008919</v>
+        <v>123008823</v>
       </c>
       <c r="B14" t="n">
-        <v>8441</v>
+        <v>5173</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2413,21 +2409,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2436,20 +2432,24 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566404</v>
+        <v>566444</v>
       </c>
       <c r="R14" t="n">
-        <v>6584083</v>
+        <v>6583992</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2516,17 +2516,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -5589,10 +5589,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123598850</v>
+        <v>123607777</v>
       </c>
       <c r="B40" t="n">
-        <v>57497</v>
+        <v>57634</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5605,21 +5605,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5627,7 +5627,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5637,13 +5637,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566443</v>
+        <v>566358</v>
       </c>
       <c r="R40" t="n">
-        <v>6584034</v>
+        <v>6584063</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5699,10 +5699,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123607777</v>
+        <v>123598850</v>
       </c>
       <c r="B41" t="n">
-        <v>57634</v>
+        <v>57497</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5715,21 +5715,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5737,7 +5737,7 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5747,13 +5747,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566358</v>
+        <v>566443</v>
       </c>
       <c r="R41" t="n">
-        <v>6584063</v>
+        <v>6584034</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122924069</v>
+        <v>122924063</v>
       </c>
       <c r="B2" t="n">
-        <v>95150</v>
+        <v>57503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566445</v>
+        <v>566588</v>
       </c>
       <c r="R2" t="n">
-        <v>6584241</v>
+        <v>6584418</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -775,18 +775,12 @@
           <t>14:00</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Växer under martallar på hällmark</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -797,7 +791,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Hällmarksskog.</t>
+          <t>Äldre barrskog.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -818,7 +812,7 @@
         <v>122924806</v>
       </c>
       <c r="B3" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -949,10 +943,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122924063</v>
+        <v>122924906</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>56697</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -961,25 +955,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -987,7 +981,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -997,14 +991,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öster om Höghäll, Slätthagen, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566588</v>
+        <v>566411</v>
       </c>
       <c r="R4" t="n">
-        <v>6584418</v>
+        <v>6584027</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1036,7 +1030,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1046,7 +1040,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>spillning i äldre hälimarksskog. Skogen är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,7 +1064,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Äldre barrskog.</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1083,10 +1082,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122924072</v>
+        <v>122925010</v>
       </c>
       <c r="B5" t="n">
-        <v>8441</v>
+        <v>56697</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1099,30 +1098,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1132,14 +1130,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öster om Höghäll, Slätthagen, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>566430</v>
       </c>
       <c r="R5" t="n">
-        <v>6584245</v>
+        <v>6584038</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1171,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1181,12 +1179,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gnagspår på tallåga i hällmark</t>
+          <t>Spillning i äldre hällmarksskog. Skogen är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,7 +1193,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1207,21 +1204,6 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1239,10 +1221,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122924036</v>
+        <v>122924072</v>
       </c>
       <c r="B6" t="n">
-        <v>105485</v>
+        <v>8445</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1255,31 +1237,32 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1287,14 +1270,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sydost om Höghäll, Slätthagen, Srm</t>
+          <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566654</v>
+        <v>566430</v>
       </c>
       <c r="R6" t="n">
-        <v>6584502</v>
+        <v>6584245</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1326,7 +1309,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1336,7 +1319,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gnagspår på tallåga i hällmark</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1356,7 +1344,22 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrskog. Kontinutietsskog</t>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1374,10 +1377,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122925010</v>
+        <v>122924036</v>
       </c>
       <c r="B7" t="n">
-        <v>56691</v>
+        <v>105502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1390,31 +1393,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1422,14 +1425,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Sydost om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566430</v>
+        <v>566654</v>
       </c>
       <c r="R7" t="n">
-        <v>6584038</v>
+        <v>6584502</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1461,7 +1464,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1471,12 +1474,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spillning i äldre hällmarksskog. Skogen är avverkningsanmäld.</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1485,6 +1483,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1495,7 +1494,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Barrskog. Kontinutietsskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1513,10 +1512,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122924906</v>
+        <v>122924069</v>
       </c>
       <c r="B8" t="n">
-        <v>56691</v>
+        <v>95167</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1529,46 +1528,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566411</v>
+        <v>566445</v>
       </c>
       <c r="R8" t="n">
-        <v>6584027</v>
+        <v>6584241</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1600,7 +1599,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1610,12 +1609,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>spillning i äldre hälimarksskog. Skogen är avverkningsanmäld.</t>
+          <t>Växer under martallar på hällmark</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1624,6 +1623,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Hällmarksskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1652,10 +1652,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123008173</v>
+        <v>123009148</v>
       </c>
       <c r="B9" t="n">
-        <v>8441</v>
+        <v>79399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1664,34 +1664,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1701,10 +1699,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566354</v>
+        <v>566372</v>
       </c>
       <c r="R9" t="n">
-        <v>6584152</v>
+        <v>6584091</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1736,7 +1734,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1746,7 +1744,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Substrat är gammal tallstubbe i hällmark.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1799,10 +1802,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123010595</v>
+        <v>123009266</v>
       </c>
       <c r="B10" t="n">
-        <v>8441</v>
+        <v>8445</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1841,17 +1844,21 @@
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lövlunda, Lövlunda, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566008</v>
+        <v>566408</v>
       </c>
       <c r="R10" t="n">
-        <v>6583487</v>
+        <v>6584004</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1883,7 +1890,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1893,7 +1900,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1913,7 +1920,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Hälmarksskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1946,10 +1953,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123007993</v>
+        <v>123008304</v>
       </c>
       <c r="B11" t="n">
-        <v>8441</v>
+        <v>57503</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1958,34 +1965,33 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1995,14 +2001,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Slätthagen, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566400</v>
+        <v>566374</v>
       </c>
       <c r="R11" t="n">
-        <v>6584187</v>
+        <v>6584013</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2034,7 +2040,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2044,7 +2050,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på stående död tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2053,7 +2064,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2065,21 +2075,6 @@
       <c r="AI11" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2097,10 +2092,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123011004</v>
+        <v>123007993</v>
       </c>
       <c r="B12" t="n">
-        <v>57497</v>
+        <v>8445</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2109,33 +2104,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2145,14 +2141,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lövlunda, Lövlunda, Srm</t>
+          <t>Söder om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566010</v>
+        <v>566400</v>
       </c>
       <c r="R12" t="n">
-        <v>6583585</v>
+        <v>6584187</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2184,7 +2180,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2194,7 +2190,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2203,6 +2199,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2213,22 +2210,22 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Äldre barrskogsmiljö</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2246,10 +2243,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123008919</v>
+        <v>123011004</v>
       </c>
       <c r="B13" t="n">
-        <v>8441</v>
+        <v>57503</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2258,47 +2255,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Lövlunda, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566404</v>
+        <v>566010</v>
       </c>
       <c r="R13" t="n">
-        <v>6584083</v>
+        <v>6583585</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2349,7 +2349,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2360,22 +2359,22 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Äldre barrskogsmiljö</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2393,10 +2392,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123008823</v>
+        <v>123003959</v>
       </c>
       <c r="B14" t="n">
-        <v>5173</v>
+        <v>57503</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2405,54 +2404,53 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566444</v>
+        <v>566582</v>
       </c>
       <c r="R14" t="n">
-        <v>6583992</v>
+        <v>6584418</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2476,22 +2474,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2500,54 +2488,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123003959</v>
+        <v>123008919</v>
       </c>
       <c r="B15" t="n">
-        <v>57497</v>
+        <v>8445</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2556,53 +2518,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566582</v>
+        <v>566404</v>
       </c>
       <c r="R15" t="n">
-        <v>6584418</v>
+        <v>6584083</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2626,12 +2585,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2640,28 +2609,54 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123009148</v>
+        <v>123008823</v>
       </c>
       <c r="B16" t="n">
-        <v>79393</v>
+        <v>5174</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2670,45 +2665,51 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566372</v>
+        <v>566444</v>
       </c>
       <c r="R16" t="n">
-        <v>6584091</v>
+        <v>6583992</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2753,11 +2754,6 @@
           <t>13:00</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Substrat är gammal tallstubbe i hällmark.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2780,17 +2776,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2808,10 +2804,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123008304</v>
+        <v>123008173</v>
       </c>
       <c r="B17" t="n">
-        <v>57497</v>
+        <v>8445</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2820,50 +2816,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566374</v>
+        <v>566354</v>
       </c>
       <c r="R17" t="n">
-        <v>6584013</v>
+        <v>6584152</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2895,7 +2888,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2905,12 +2898,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska hackmärken på stående död tall.</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2919,6 +2907,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2930,6 +2919,21 @@
       <c r="AI17" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2947,10 +2951,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123009266</v>
+        <v>123010595</v>
       </c>
       <c r="B18" t="n">
-        <v>8441</v>
+        <v>8445</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2989,21 +2993,17 @@
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Lövlunda, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566408</v>
+        <v>566008</v>
       </c>
       <c r="R18" t="n">
-        <v>6584004</v>
+        <v>6583487</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Hälmarksskog</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -3098,10 +3098,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123033108</v>
+        <v>123003070</v>
       </c>
       <c r="B19" t="n">
-        <v>97333</v>
+        <v>56697</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3114,41 +3114,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566666</v>
+        <v>566462</v>
       </c>
       <c r="R19" t="n">
-        <v>6584456</v>
+        <v>6584262</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3175,18 +3179,27 @@
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3205,10 +3218,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123003070</v>
+        <v>123033108</v>
       </c>
       <c r="B20" t="n">
-        <v>56691</v>
+        <v>97350</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3221,45 +3234,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Morfars trappa, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566462</v>
+        <v>566666</v>
       </c>
       <c r="R20" t="n">
-        <v>6584262</v>
+        <v>6584456</v>
       </c>
       <c r="S20" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3286,27 +3295,18 @@
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-09</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3325,10 +3325,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123050079</v>
+        <v>123034725</v>
       </c>
       <c r="B21" t="n">
-        <v>98379</v>
+        <v>5174</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3337,53 +3337,50 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Farfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566634</v>
+        <v>566550</v>
       </c>
       <c r="R21" t="n">
-        <v>6584453</v>
+        <v>6584397</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3407,22 +3404,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3431,18 +3418,19 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3452,7 +3440,7 @@
         <v>123033899</v>
       </c>
       <c r="B22" t="n">
-        <v>5173</v>
+        <v>5174</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3561,10 +3549,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123034725</v>
+        <v>123050079</v>
       </c>
       <c r="B23" t="n">
-        <v>5173</v>
+        <v>98396</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3573,50 +3561,53 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Farfars trappa, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566550</v>
+        <v>566634</v>
       </c>
       <c r="R23" t="n">
-        <v>6584397</v>
+        <v>6584453</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3640,12 +3631,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3654,29 +3655,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123080901</v>
+        <v>123077638</v>
       </c>
       <c r="B24" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3716,27 +3716,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566636</v>
+        <v>566640</v>
       </c>
       <c r="R24" t="n">
-        <v>6584458</v>
+        <v>6584477</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3783,7 +3775,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Knärot i äldre barrskog med vinterståndare.</t>
+          <t>Växer längs den gamla kyrkstigen i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3803,7 +3795,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Äldre barrskog. Kontinuitetsskog</t>
+          <t>Äldre barrskogsmiljö</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3821,10 +3813,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123077638</v>
+        <v>123079585</v>
       </c>
       <c r="B25" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3856,7 +3848,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3873,13 +3865,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566640</v>
+        <v>566632</v>
       </c>
       <c r="R25" t="n">
-        <v>6584477</v>
+        <v>6584462</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3908,7 +3900,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3918,12 +3910,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Växer längs den gamla kyrkstigen i äldre barrskog.</t>
+          <t>Växer i mossrik äldre barrskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3943,7 +3935,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Äldre barrskogsmiljö</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3964,7 +3956,7 @@
         <v>123080289</v>
       </c>
       <c r="B26" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4088,10 +4080,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123079585</v>
+        <v>123080901</v>
       </c>
       <c r="B27" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4123,7 +4115,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4131,22 +4123,30 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566632</v>
+        <v>566636</v>
       </c>
       <c r="R27" t="n">
-        <v>6584462</v>
+        <v>6584458</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Växer i mossrik äldre barrskog.</t>
+          <t>Knärot i äldre barrskog med vinterståndare.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskog. Kontinuitetsskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123231344</v>
+        <v>123185939</v>
       </c>
       <c r="B28" t="n">
-        <v>8441</v>
+        <v>8445</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4261,7 +4261,11 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -4273,17 +4277,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566775</v>
+        <v>566060</v>
       </c>
       <c r="R28" t="n">
-        <v>6584532</v>
+        <v>6583553</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4307,22 +4311,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4331,29 +4335,28 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123241264</v>
+        <v>123232797</v>
       </c>
       <c r="B29" t="n">
-        <v>57497</v>
+        <v>8434</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4362,33 +4365,34 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4398,10 +4402,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566553</v>
+        <v>566699</v>
       </c>
       <c r="R29" t="n">
-        <v>6584351</v>
+        <v>6584476</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4431,17 +4435,28 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4460,10 +4475,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123232797</v>
+        <v>123231344</v>
       </c>
       <c r="B30" t="n">
-        <v>8430</v>
+        <v>8445</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4476,21 +4491,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4509,10 +4524,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566699</v>
+        <v>566775</v>
       </c>
       <c r="R30" t="n">
-        <v>6584476</v>
+        <v>6584532</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4544,7 +4559,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4554,7 +4569,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4582,10 +4597,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123185939</v>
+        <v>123241264</v>
       </c>
       <c r="B31" t="n">
-        <v>8441</v>
+        <v>57503</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4594,54 +4609,49 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lövlunda, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566060</v>
+        <v>566553</v>
       </c>
       <c r="R31" t="n">
-        <v>6583553</v>
+        <v>6584351</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4665,22 +4675,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:23</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12:23</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4695,12 +4695,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4710,7 +4710,7 @@
         <v>123236226</v>
       </c>
       <c r="B32" t="n">
-        <v>90931</v>
+        <v>90948</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>123271947</v>
       </c>
       <c r="B33" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>123527972</v>
       </c>
       <c r="B34" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>123547348</v>
       </c>
       <c r="B35" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>123559251</v>
       </c>
       <c r="B36" t="n">
-        <v>5173</v>
+        <v>5174</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>123560721</v>
       </c>
       <c r="B37" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5376,10 +5376,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123599223</v>
+        <v>123598850</v>
       </c>
       <c r="B38" t="n">
-        <v>8430</v>
+        <v>57503</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5388,34 +5388,33 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5425,10 +5424,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566441</v>
+        <v>566443</v>
       </c>
       <c r="R38" t="n">
-        <v>6583991</v>
+        <v>6584034</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5469,7 +5468,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5488,10 +5486,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123607157</v>
+        <v>123607777</v>
       </c>
       <c r="B39" t="n">
-        <v>91363</v>
+        <v>57640</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5504,21 +5502,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6040162</v>
+        <v>103021</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5526,13 +5534,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566318</v>
+        <v>566358</v>
       </c>
       <c r="R39" t="n">
-        <v>6584044</v>
+        <v>6584063</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5570,7 +5578,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5589,10 +5596,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123607777</v>
+        <v>123599090</v>
       </c>
       <c r="B40" t="n">
-        <v>57634</v>
+        <v>5174</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5601,33 +5608,34 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5637,13 +5645,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566358</v>
+        <v>566441</v>
       </c>
       <c r="R40" t="n">
-        <v>6584063</v>
+        <v>6583991</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5681,6 +5689,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5699,10 +5708,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123598850</v>
+        <v>123607303</v>
       </c>
       <c r="B41" t="n">
-        <v>57497</v>
+        <v>8445</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5711,33 +5720,34 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5747,10 +5757,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566443</v>
+        <v>566318</v>
       </c>
       <c r="R41" t="n">
-        <v>6584034</v>
+        <v>6584044</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5791,6 +5801,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5809,10 +5820,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123607303</v>
+        <v>123599223</v>
       </c>
       <c r="B42" t="n">
-        <v>8441</v>
+        <v>8434</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5825,21 +5836,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5858,10 +5869,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566318</v>
+        <v>566441</v>
       </c>
       <c r="R42" t="n">
-        <v>6584044</v>
+        <v>6583991</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5921,10 +5932,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123599090</v>
+        <v>123607157</v>
       </c>
       <c r="B43" t="n">
-        <v>5173</v>
+        <v>91380</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5933,36 +5944,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5970,10 +5970,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>566441</v>
+        <v>566318</v>
       </c>
       <c r="R43" t="n">
-        <v>6583991</v>
+        <v>6584044</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6031,6 +6031,336 @@
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>123783535</v>
+      </c>
+      <c r="B44" t="n">
+        <v>5174</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Björnsten, Srm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>566702</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6584466</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>123783601</v>
+      </c>
+      <c r="B45" t="n">
+        <v>90948</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Morfars trappa, Srm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>566212</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6583882</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>123784683</v>
+      </c>
+      <c r="B46" t="n">
+        <v>5194</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lövlunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>566011</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6583560</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -3101,7 +3101,7 @@
         <v>123003070</v>
       </c>
       <c r="B19" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3218,10 +3218,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123033108</v>
+        <v>123050079</v>
       </c>
       <c r="B20" t="n">
-        <v>97350</v>
+        <v>98502</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3230,29 +3230,37 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -3262,13 +3270,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566666</v>
+        <v>566634</v>
       </c>
       <c r="R20" t="n">
-        <v>6584456</v>
+        <v>6584453</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3292,12 +3300,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3306,19 +3324,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anja Hynynen, Emelie Bergermark</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3328,7 +3345,7 @@
         <v>123034725</v>
       </c>
       <c r="B21" t="n">
-        <v>5174</v>
+        <v>5176</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3440,7 +3457,7 @@
         <v>123033899</v>
       </c>
       <c r="B22" t="n">
-        <v>5174</v>
+        <v>5176</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3549,10 +3566,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123050079</v>
+        <v>123033108</v>
       </c>
       <c r="B23" t="n">
-        <v>98396</v>
+        <v>97367</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3561,37 +3578,29 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3601,13 +3610,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566634</v>
+        <v>566666</v>
       </c>
       <c r="R23" t="n">
-        <v>6584453</v>
+        <v>6584456</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3631,22 +3640,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3655,28 +3654,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Emelie Bergermark, Anja Hynynen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123077638</v>
+        <v>123080901</v>
       </c>
       <c r="B24" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3716,19 +3716,27 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566640</v>
+        <v>566636</v>
       </c>
       <c r="R24" t="n">
-        <v>6584477</v>
+        <v>6584458</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3775,7 +3783,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Växer längs den gamla kyrkstigen i äldre barrskog.</t>
+          <t>Knärot i äldre barrskog med vinterståndare.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3795,7 +3803,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Äldre barrskogsmiljö</t>
+          <t>Äldre barrskog. Kontinuitetsskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3816,7 +3824,7 @@
         <v>123079585</v>
       </c>
       <c r="B25" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3953,10 +3961,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123080289</v>
+        <v>123077638</v>
       </c>
       <c r="B26" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3986,8 +3994,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3997,10 +4013,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566632</v>
+        <v>566640</v>
       </c>
       <c r="R26" t="n">
-        <v>6584457</v>
+        <v>6584477</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4032,7 +4048,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4042,7 +4058,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Växer längs den gamla kyrkstigen i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4062,7 +4083,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Äldre barrskog.</t>
+          <t>Äldre barrskogsmiljö</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4080,10 +4101,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123080901</v>
+        <v>123080289</v>
       </c>
       <c r="B27" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4113,37 +4134,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566636</v>
+        <v>566632</v>
       </c>
       <c r="R27" t="n">
-        <v>6584458</v>
+        <v>6584457</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4175,7 +4180,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4185,12 +4190,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Knärot i äldre barrskog med vinterståndare.</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Äldre barrskog. Kontinuitetsskog</t>
+          <t>Äldre barrskog.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4231,7 +4231,7 @@
         <v>123185939</v>
       </c>
       <c r="B28" t="n">
-        <v>8445</v>
+        <v>8447</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>123232797</v>
       </c>
       <c r="B29" t="n">
-        <v>8434</v>
+        <v>8436</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4475,10 +4475,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123231344</v>
+        <v>123241264</v>
       </c>
       <c r="B30" t="n">
-        <v>8445</v>
+        <v>57506</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4487,34 +4487,33 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4524,10 +4523,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566775</v>
+        <v>566553</v>
       </c>
       <c r="R30" t="n">
-        <v>6584532</v>
+        <v>6584351</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4557,28 +4556,17 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4597,10 +4585,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123241264</v>
+        <v>123231344</v>
       </c>
       <c r="B31" t="n">
-        <v>57503</v>
+        <v>8447</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4609,33 +4597,34 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4645,10 +4634,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566553</v>
+        <v>566775</v>
       </c>
       <c r="R31" t="n">
-        <v>6584351</v>
+        <v>6584532</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4678,17 +4667,28 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4710,7 +4710,7 @@
         <v>123236226</v>
       </c>
       <c r="B32" t="n">
-        <v>90948</v>
+        <v>90953</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>123271947</v>
       </c>
       <c r="B33" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>123527972</v>
       </c>
       <c r="B34" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>123547348</v>
       </c>
       <c r="B35" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>123559251</v>
       </c>
       <c r="B36" t="n">
-        <v>5174</v>
+        <v>5176</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>123560721</v>
       </c>
       <c r="B37" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5376,10 +5376,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123598850</v>
+        <v>123599090</v>
       </c>
       <c r="B38" t="n">
-        <v>57503</v>
+        <v>5176</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5388,33 +5388,34 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5424,10 +5425,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566443</v>
+        <v>566441</v>
       </c>
       <c r="R38" t="n">
-        <v>6584034</v>
+        <v>6583991</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5468,6 +5469,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5486,10 +5488,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123607777</v>
+        <v>123598850</v>
       </c>
       <c r="B39" t="n">
-        <v>57640</v>
+        <v>57506</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5502,21 +5504,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5524,7 +5526,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5534,13 +5536,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566358</v>
+        <v>566443</v>
       </c>
       <c r="R39" t="n">
-        <v>6584063</v>
+        <v>6584034</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5596,10 +5598,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123599090</v>
+        <v>123599223</v>
       </c>
       <c r="B40" t="n">
-        <v>5174</v>
+        <v>8436</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5612,21 +5614,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5711,7 +5713,7 @@
         <v>123607303</v>
       </c>
       <c r="B41" t="n">
-        <v>8445</v>
+        <v>8447</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5820,10 +5822,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123599223</v>
+        <v>123607777</v>
       </c>
       <c r="B42" t="n">
-        <v>8434</v>
+        <v>57643</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5832,34 +5834,33 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5869,13 +5870,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566441</v>
+        <v>566358</v>
       </c>
       <c r="R42" t="n">
-        <v>6583991</v>
+        <v>6584063</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5913,7 +5914,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5935,7 +5935,7 @@
         <v>123607157</v>
       </c>
       <c r="B43" t="n">
-        <v>91380</v>
+        <v>91385</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>123783535</v>
       </c>
       <c r="B44" t="n">
-        <v>5174</v>
+        <v>5176</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>123783601</v>
       </c>
       <c r="B45" t="n">
-        <v>90948</v>
+        <v>90953</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>123784683</v>
       </c>
       <c r="B46" t="n">
-        <v>5194</v>
+        <v>5196</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -3673,10 +3673,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123080901</v>
+        <v>123080289</v>
       </c>
       <c r="B24" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3706,37 +3706,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566636</v>
+        <v>566632</v>
       </c>
       <c r="R24" t="n">
-        <v>6584458</v>
+        <v>6584457</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3768,7 +3752,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3778,12 +3762,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Knärot i äldre barrskog med vinterståndare.</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3803,7 +3782,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Äldre barrskog. Kontinuitetsskog</t>
+          <t>Äldre barrskog.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3821,10 +3800,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123079585</v>
+        <v>123077638</v>
       </c>
       <c r="B25" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3856,7 +3835,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3873,13 +3852,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566632</v>
+        <v>566640</v>
       </c>
       <c r="R25" t="n">
-        <v>6584462</v>
+        <v>6584477</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3908,7 +3887,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3918,12 +3897,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Växer i mossrik äldre barrskog.</t>
+          <t>Växer längs den gamla kyrkstigen i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3943,7 +3922,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskogsmiljö</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3961,10 +3940,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123077638</v>
+        <v>123079585</v>
       </c>
       <c r="B26" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3996,7 +3975,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4013,13 +3992,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566640</v>
+        <v>566632</v>
       </c>
       <c r="R26" t="n">
-        <v>6584477</v>
+        <v>6584462</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4048,7 +4027,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4058,12 +4037,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Växer längs den gamla kyrkstigen i äldre barrskog.</t>
+          <t>Växer i mossrik äldre barrskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4083,7 +4062,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Äldre barrskogsmiljö</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4101,10 +4080,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123080289</v>
+        <v>123080901</v>
       </c>
       <c r="B27" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4134,21 +4113,37 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Öster om Höghäll, Slätthagen, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566632</v>
+        <v>566636</v>
       </c>
       <c r="R27" t="n">
-        <v>6584457</v>
+        <v>6584458</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4180,7 +4175,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4190,7 +4185,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Knärot i äldre barrskog med vinterståndare.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Äldre barrskog.</t>
+          <t>Äldre barrskog. Kontinuitetsskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4478,7 +4478,7 @@
         <v>123241264</v>
       </c>
       <c r="B30" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>123236226</v>
       </c>
       <c r="B32" t="n">
-        <v>90953</v>
+        <v>90955</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>123271947</v>
       </c>
       <c r="B33" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>123527972</v>
       </c>
       <c r="B34" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5154,10 +5154,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123559251</v>
+        <v>123560721</v>
       </c>
       <c r="B36" t="n">
-        <v>5176</v>
+        <v>56700</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5170,30 +5170,29 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5203,10 +5202,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566381</v>
+        <v>566420</v>
       </c>
       <c r="R36" t="n">
-        <v>6584122</v>
+        <v>6584088</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5247,7 +5246,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5266,10 +5264,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123560721</v>
+        <v>123559251</v>
       </c>
       <c r="B37" t="n">
-        <v>56700</v>
+        <v>5176</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5282,29 +5280,30 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5314,10 +5313,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>566420</v>
+        <v>566381</v>
       </c>
       <c r="R37" t="n">
-        <v>6584088</v>
+        <v>6584122</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5358,6 +5357,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5376,10 +5376,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123599090</v>
+        <v>123599223</v>
       </c>
       <c r="B38" t="n">
-        <v>5176</v>
+        <v>8436</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5392,21 +5392,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5491,7 +5491,7 @@
         <v>123598850</v>
       </c>
       <c r="B39" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5598,10 +5598,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123599223</v>
+        <v>123607777</v>
       </c>
       <c r="B40" t="n">
-        <v>8436</v>
+        <v>57644</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5610,34 +5610,33 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5647,13 +5646,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566441</v>
+        <v>566358</v>
       </c>
       <c r="R40" t="n">
-        <v>6583991</v>
+        <v>6584063</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5691,7 +5690,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5710,10 +5708,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123607303</v>
+        <v>123599090</v>
       </c>
       <c r="B41" t="n">
-        <v>8447</v>
+        <v>5176</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5726,21 +5724,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5759,10 +5757,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566318</v>
+        <v>566441</v>
       </c>
       <c r="R41" t="n">
-        <v>6584044</v>
+        <v>6583991</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5822,10 +5820,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123607777</v>
+        <v>123607303</v>
       </c>
       <c r="B42" t="n">
-        <v>57643</v>
+        <v>8447</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5834,33 +5832,34 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5870,13 +5869,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566358</v>
+        <v>566318</v>
       </c>
       <c r="R42" t="n">
-        <v>6584063</v>
+        <v>6584044</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5914,6 +5913,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5935,7 +5935,7 @@
         <v>123607157</v>
       </c>
       <c r="B43" t="n">
-        <v>91385</v>
+        <v>91387</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6033,10 +6033,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123783535</v>
+        <v>123784683</v>
       </c>
       <c r="B44" t="n">
-        <v>5176</v>
+        <v>5196</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6049,21 +6049,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6078,14 +6078,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>566702</v>
+        <v>566011</v>
       </c>
       <c r="R44" t="n">
-        <v>6584466</v>
+        <v>6583560</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6145,10 +6145,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123783601</v>
+        <v>123783535</v>
       </c>
       <c r="B45" t="n">
-        <v>90953</v>
+        <v>5176</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6161,37 +6161,43 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Morfars trappa, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>566212</v>
+        <v>566702</v>
       </c>
       <c r="R45" t="n">
-        <v>6583882</v>
+        <v>6584466</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6251,10 +6257,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123784683</v>
+        <v>123783601</v>
       </c>
       <c r="B46" t="n">
-        <v>5196</v>
+        <v>90955</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6267,43 +6273,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lövlunda, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>566011</v>
+        <v>566212</v>
       </c>
       <c r="R46" t="n">
-        <v>6583560</v>
+        <v>6583882</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4228,10 +4228,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123185939</v>
+        <v>123241264</v>
       </c>
       <c r="B28" t="n">
-        <v>8447</v>
+        <v>57507</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4240,54 +4240,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lövlunda, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566060</v>
+        <v>566553</v>
       </c>
       <c r="R28" t="n">
-        <v>6583553</v>
+        <v>6584351</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4311,22 +4306,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>12:23</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>12:23</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4341,12 +4326,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4475,10 +4460,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123241264</v>
+        <v>123185939</v>
       </c>
       <c r="B30" t="n">
-        <v>57507</v>
+        <v>8447</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4487,49 +4472,54 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566553</v>
+        <v>566060</v>
       </c>
       <c r="R30" t="n">
-        <v>6584351</v>
+        <v>6583553</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4553,12 +4543,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4573,12 +4573,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4932,7 +4932,7 @@
         <v>123527972</v>
       </c>
       <c r="B34" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5376,10 +5376,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123599223</v>
+        <v>123599090</v>
       </c>
       <c r="B38" t="n">
-        <v>8436</v>
+        <v>5176</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5392,21 +5392,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123607777</v>
+        <v>123599223</v>
       </c>
       <c r="B40" t="n">
-        <v>57644</v>
+        <v>8436</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5610,33 +5610,34 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5646,13 +5647,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566358</v>
+        <v>566441</v>
       </c>
       <c r="R40" t="n">
-        <v>6584063</v>
+        <v>6583991</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5690,6 +5691,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5708,10 +5710,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123599090</v>
+        <v>123607303</v>
       </c>
       <c r="B41" t="n">
-        <v>5176</v>
+        <v>8447</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5724,21 +5726,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5757,10 +5759,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566441</v>
+        <v>566318</v>
       </c>
       <c r="R41" t="n">
-        <v>6583991</v>
+        <v>6584044</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5820,10 +5822,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123607303</v>
+        <v>123607777</v>
       </c>
       <c r="B42" t="n">
-        <v>8447</v>
+        <v>57644</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5832,34 +5834,33 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5869,13 +5870,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566318</v>
+        <v>566358</v>
       </c>
       <c r="R42" t="n">
-        <v>6584044</v>
+        <v>6584063</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5913,7 +5914,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -6033,10 +6033,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123784683</v>
+        <v>123783535</v>
       </c>
       <c r="B44" t="n">
-        <v>5196</v>
+        <v>5176</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6049,21 +6049,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6078,14 +6078,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lövlunda, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>566011</v>
+        <v>566702</v>
       </c>
       <c r="R44" t="n">
-        <v>6583560</v>
+        <v>6584466</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6145,10 +6145,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123783535</v>
+        <v>123790035</v>
       </c>
       <c r="B45" t="n">
-        <v>5176</v>
+        <v>56449</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6161,46 +6161,50 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100526</v>
+        <v>208255</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Hällarna vid kraftledningsgatan, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>566702</v>
+        <v>566426</v>
       </c>
       <c r="R45" t="n">
-        <v>6584466</v>
+        <v>6584234</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6245,22 +6249,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123783601</v>
+        <v>123784683</v>
       </c>
       <c r="B46" t="n">
-        <v>90955</v>
+        <v>5196</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6273,37 +6277,43 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Morfars trappa, Srm</t>
+          <t>Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>566212</v>
+        <v>566011</v>
       </c>
       <c r="R46" t="n">
-        <v>6583882</v>
+        <v>6583560</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6360,6 +6370,112 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>123783601</v>
+      </c>
+      <c r="B47" t="n">
+        <v>90955</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Morfars trappa, Srm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>566212</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6583882</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -5710,10 +5710,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123607303</v>
+        <v>123607777</v>
       </c>
       <c r="B41" t="n">
-        <v>8447</v>
+        <v>57644</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5722,34 +5722,33 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5759,13 +5758,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566318</v>
+        <v>566358</v>
       </c>
       <c r="R41" t="n">
-        <v>6584044</v>
+        <v>6584063</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5803,7 +5802,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5822,10 +5820,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123607777</v>
+        <v>123607303</v>
       </c>
       <c r="B42" t="n">
-        <v>57644</v>
+        <v>8447</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5834,33 +5832,34 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5870,13 +5869,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566358</v>
+        <v>566318</v>
       </c>
       <c r="R42" t="n">
-        <v>6584063</v>
+        <v>6584044</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5914,6 +5913,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -5154,10 +5154,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123560721</v>
+        <v>123559251</v>
       </c>
       <c r="B36" t="n">
-        <v>56700</v>
+        <v>5176</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5170,29 +5170,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5202,10 +5203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566420</v>
+        <v>566381</v>
       </c>
       <c r="R36" t="n">
-        <v>6584088</v>
+        <v>6584122</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5246,6 +5247,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5264,10 +5266,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123559251</v>
+        <v>123560721</v>
       </c>
       <c r="B37" t="n">
-        <v>5176</v>
+        <v>56700</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5280,30 +5282,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5313,10 +5314,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>566381</v>
+        <v>566420</v>
       </c>
       <c r="R37" t="n">
-        <v>6584122</v>
+        <v>6584088</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5357,7 +5358,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5598,10 +5598,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123599223</v>
+        <v>123607303</v>
       </c>
       <c r="B40" t="n">
-        <v>8436</v>
+        <v>8447</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5614,21 +5614,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5647,10 +5647,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566441</v>
+        <v>566318</v>
       </c>
       <c r="R40" t="n">
-        <v>6583991</v>
+        <v>6584044</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5820,10 +5820,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123607303</v>
+        <v>123599223</v>
       </c>
       <c r="B42" t="n">
-        <v>8447</v>
+        <v>8436</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5836,21 +5836,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566318</v>
+        <v>566441</v>
       </c>
       <c r="R42" t="n">
-        <v>6584044</v>
+        <v>6583991</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6033,10 +6033,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123783535</v>
+        <v>123784683</v>
       </c>
       <c r="B44" t="n">
-        <v>5176</v>
+        <v>5196</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6049,21 +6049,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6078,14 +6078,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>566702</v>
+        <v>566011</v>
       </c>
       <c r="R44" t="n">
-        <v>6584466</v>
+        <v>6583560</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6261,10 +6261,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123784683</v>
+        <v>123783535</v>
       </c>
       <c r="B46" t="n">
-        <v>5196</v>
+        <v>5176</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6277,21 +6277,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6306,14 +6306,14 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lövlunda, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>566011</v>
+        <v>566702</v>
       </c>
       <c r="R46" t="n">
-        <v>6583560</v>
+        <v>6584466</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -5154,10 +5154,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123559251</v>
+        <v>123560721</v>
       </c>
       <c r="B36" t="n">
-        <v>5176</v>
+        <v>56700</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5170,30 +5170,29 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5203,10 +5202,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566381</v>
+        <v>566420</v>
       </c>
       <c r="R36" t="n">
-        <v>6584122</v>
+        <v>6584088</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5247,7 +5246,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5266,10 +5264,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123560721</v>
+        <v>123559251</v>
       </c>
       <c r="B37" t="n">
-        <v>56700</v>
+        <v>5176</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5282,29 +5280,30 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5314,10 +5313,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>566420</v>
+        <v>566381</v>
       </c>
       <c r="R37" t="n">
-        <v>6584088</v>
+        <v>6584122</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5358,6 +5357,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5598,10 +5598,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123607303</v>
+        <v>123599223</v>
       </c>
       <c r="B40" t="n">
-        <v>8447</v>
+        <v>8436</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5614,21 +5614,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5647,10 +5647,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566318</v>
+        <v>566441</v>
       </c>
       <c r="R40" t="n">
-        <v>6584044</v>
+        <v>6583991</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5820,10 +5820,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123599223</v>
+        <v>123607303</v>
       </c>
       <c r="B42" t="n">
-        <v>8436</v>
+        <v>8447</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5836,21 +5836,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566441</v>
+        <v>566318</v>
       </c>
       <c r="R42" t="n">
-        <v>6583991</v>
+        <v>6584044</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6145,10 +6145,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123790035</v>
+        <v>123783535</v>
       </c>
       <c r="B45" t="n">
-        <v>56449</v>
+        <v>5176</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6161,50 +6161,46 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>208255</v>
+        <v>100526</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hällarna vid kraftledningsgatan, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>566426</v>
+        <v>566702</v>
       </c>
       <c r="R45" t="n">
-        <v>6584234</v>
+        <v>6584466</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6249,22 +6245,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123783535</v>
+        <v>123790035</v>
       </c>
       <c r="B46" t="n">
-        <v>5176</v>
+        <v>56449</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6277,46 +6273,50 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100526</v>
+        <v>208255</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Hällarna vid kraftledningsgatan, Srm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>566702</v>
+        <v>566426</v>
       </c>
       <c r="R46" t="n">
-        <v>6584466</v>
+        <v>6584234</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6361,12 +6361,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -5154,10 +5154,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123560721</v>
+        <v>123559251</v>
       </c>
       <c r="B36" t="n">
-        <v>56700</v>
+        <v>5176</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5170,29 +5170,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5202,10 +5203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566420</v>
+        <v>566381</v>
       </c>
       <c r="R36" t="n">
-        <v>6584088</v>
+        <v>6584122</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5246,6 +5247,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5264,10 +5266,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123559251</v>
+        <v>123560721</v>
       </c>
       <c r="B37" t="n">
-        <v>5176</v>
+        <v>56700</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5280,30 +5282,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5313,10 +5314,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>566381</v>
+        <v>566420</v>
       </c>
       <c r="R37" t="n">
-        <v>6584122</v>
+        <v>6584088</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5357,7 +5358,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5376,10 +5376,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123599090</v>
+        <v>123599223</v>
       </c>
       <c r="B38" t="n">
-        <v>5176</v>
+        <v>8436</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5392,21 +5392,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123599223</v>
+        <v>123607777</v>
       </c>
       <c r="B40" t="n">
-        <v>8436</v>
+        <v>57644</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5610,34 +5610,33 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5647,13 +5646,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566441</v>
+        <v>566358</v>
       </c>
       <c r="R40" t="n">
-        <v>6583991</v>
+        <v>6584063</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5691,7 +5690,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5710,10 +5708,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123607777</v>
+        <v>123599090</v>
       </c>
       <c r="B41" t="n">
-        <v>57644</v>
+        <v>5176</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5722,33 +5720,34 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5758,13 +5757,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566358</v>
+        <v>566441</v>
       </c>
       <c r="R41" t="n">
-        <v>6584063</v>
+        <v>6583991</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5802,6 +5801,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -6033,10 +6033,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123790035</v>
+        <v>123784683</v>
       </c>
       <c r="B44" t="n">
-        <v>56471</v>
+        <v>5196</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6049,50 +6049,46 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>208255</v>
+        <v>105930</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hällarna vid kraftledningsgatan, Srm</t>
+          <t>Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>566426</v>
+        <v>566011</v>
       </c>
       <c r="R44" t="n">
-        <v>6584234</v>
+        <v>6583560</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6137,22 +6133,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123784683</v>
+        <v>123790035</v>
       </c>
       <c r="B45" t="n">
-        <v>5196</v>
+        <v>56471</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6165,46 +6161,50 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>105930</v>
+        <v>208255</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lövlunda, Srm</t>
+          <t>Hällarna vid kraftledningsgatan, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>566011</v>
+        <v>566426</v>
       </c>
       <c r="R45" t="n">
-        <v>6583560</v>
+        <v>6584234</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6249,12 +6249,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Emelie Bergermark</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -6479,64 +6479,60 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127060592</v>
+        <v>127061455</v>
       </c>
       <c r="B48" t="n">
-        <v>98361</v>
+        <v>57459</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>102118</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>566759</v>
+        <v>566436</v>
       </c>
       <c r="R48" t="n">
-        <v>6584518</v>
+        <v>6584241</v>
       </c>
       <c r="S48" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6565,7 +6561,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>21:37</t>
+          <t>22:16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6575,7 +6571,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>21:38</t>
+          <t>22:16</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Nattskärra vid hällmarken.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6590,72 +6591,76 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127061455</v>
+        <v>127060592</v>
       </c>
       <c r="B49" t="n">
-        <v>57459</v>
+        <v>98436</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102118</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Morfars trappa, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>566436</v>
+        <v>566759</v>
       </c>
       <c r="R49" t="n">
-        <v>6584241</v>
+        <v>6584518</v>
       </c>
       <c r="S49" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6684,7 +6689,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>22:16</t>
+          <t>21:37</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6694,12 +6699,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>22:16</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Nattskärra vid hällmarken.</t>
+          <t>21:38</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6714,12 +6714,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6729,7 +6729,7 @@
         <v>127055817</v>
       </c>
       <c r="B50" t="n">
-        <v>92527</v>
+        <v>92601</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>127058906</v>
       </c>
       <c r="B52" t="n">
-        <v>92527</v>
+        <v>92601</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>127057216</v>
       </c>
       <c r="B53" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>127057091</v>
       </c>
       <c r="B54" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>127056859</v>
       </c>
       <c r="B55" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122924063</v>
+        <v>122924806</v>
       </c>
       <c r="B2" t="n">
-        <v>57503</v>
+        <v>56697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -723,14 +723,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öster om Höghäll, Slätthagen, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566588</v>
+        <v>566416</v>
       </c>
       <c r="R2" t="n">
-        <v>6584418</v>
+        <v>6584024</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +791,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Äldre barrskog.</t>
+          <t>Hällmarksskog.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -809,7 +809,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122924806</v>
+        <v>122924906</v>
       </c>
       <c r="B3" t="n">
         <v>56697</v>
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566416</v>
+        <v>566411</v>
       </c>
       <c r="R3" t="n">
-        <v>6584024</v>
+        <v>6584027</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -909,6 +909,11 @@
           <t>12:30</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>spillning i äldre hälimarksskog. Skogen är avverkningsanmäld.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -925,7 +930,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Hällmarksskog.</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -943,7 +948,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122924906</v>
+        <v>122925010</v>
       </c>
       <c r="B4" t="n">
         <v>56697</v>
@@ -981,7 +986,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -995,10 +1000,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566411</v>
+        <v>566430</v>
       </c>
       <c r="R4" t="n">
-        <v>6584027</v>
+        <v>6584038</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1045,7 +1050,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>spillning i äldre hälimarksskog. Skogen är avverkningsanmäld.</t>
+          <t>Spillning i äldre hällmarksskog. Skogen är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1082,10 +1087,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122925010</v>
+        <v>123009148</v>
       </c>
       <c r="B5" t="n">
-        <v>56697</v>
+        <v>79399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1094,50 +1099,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566430</v>
+        <v>566372</v>
       </c>
       <c r="R5" t="n">
-        <v>6584038</v>
+        <v>6584091</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spillning i äldre hällmarksskog. Skogen är avverkningsanmäld.</t>
+          <t>Substrat är gammal tallstubbe i hällmark.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1193,6 +1193,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1204,6 +1205,21 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1221,7 +1237,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122924072</v>
+        <v>123009266</v>
       </c>
       <c r="B6" t="n">
         <v>8445</v>
@@ -1270,14 +1286,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öster om Höghäll, Slätthagen, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566430</v>
+        <v>566408</v>
       </c>
       <c r="R6" t="n">
-        <v>6584245</v>
+        <v>6584004</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1309,7 +1325,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1319,12 +1335,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gnagspår på tallåga i hällmark</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1344,7 +1355,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Hälmarksskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1377,10 +1388,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122924036</v>
+        <v>123008304</v>
       </c>
       <c r="B7" t="n">
-        <v>105502</v>
+        <v>57503</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1389,35 +1400,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1425,14 +1436,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sydost om Höghäll, Slätthagen, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566654</v>
+        <v>566374</v>
       </c>
       <c r="R7" t="n">
-        <v>6584502</v>
+        <v>6584013</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1464,7 +1475,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1474,7 +1485,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på stående död tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1483,7 +1499,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1494,7 +1509,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Barrskog. Kontinutietsskog</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1512,10 +1527,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122924069</v>
+        <v>123011004</v>
       </c>
       <c r="B8" t="n">
-        <v>95167</v>
+        <v>57503</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1524,50 +1539,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Öster om Höghäll, Slätthagen, Srm</t>
+          <t>Lövlunda, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566445</v>
+        <v>566010</v>
       </c>
       <c r="R8" t="n">
-        <v>6584241</v>
+        <v>6583585</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1599,7 +1614,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1609,12 +1624,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växer under martallar på hällmark</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1623,7 +1633,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1634,7 +1643,22 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Hällmarksskog.</t>
+          <t>Äldre barrskogsmiljö</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1652,10 +1676,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123009148</v>
+        <v>123008919</v>
       </c>
       <c r="B9" t="n">
-        <v>79399</v>
+        <v>8445</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1664,32 +1688,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1699,10 +1725,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566372</v>
+        <v>566404</v>
       </c>
       <c r="R9" t="n">
-        <v>6584091</v>
+        <v>6584083</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1745,11 +1771,6 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Substrat är gammal tallstubbe i hällmark.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1802,10 +1823,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123009266</v>
+        <v>123008823</v>
       </c>
       <c r="B10" t="n">
-        <v>8445</v>
+        <v>5174</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1818,21 +1839,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1841,7 +1862,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1855,10 +1876,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566408</v>
+        <v>566444</v>
       </c>
       <c r="R10" t="n">
-        <v>6584004</v>
+        <v>6583992</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1920,22 +1941,22 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Hälmarksskog</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1953,10 +1974,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123008304</v>
+        <v>123010595</v>
       </c>
       <c r="B11" t="n">
-        <v>57503</v>
+        <v>8445</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1965,50 +1986,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Lövlunda, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566374</v>
+        <v>566008</v>
       </c>
       <c r="R11" t="n">
-        <v>6584013</v>
+        <v>6583487</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2040,7 +2058,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2050,12 +2068,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska hackmärken på stående död tall.</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2064,6 +2077,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2075,6 +2089,21 @@
       <c r="AI11" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2092,10 +2121,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123007993</v>
+        <v>123033899</v>
       </c>
       <c r="B12" t="n">
-        <v>8445</v>
+        <v>5176</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2108,21 +2137,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2134,24 +2163,20 @@
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Slätthagen, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566400</v>
+        <v>566802</v>
       </c>
       <c r="R12" t="n">
-        <v>6584187</v>
+        <v>6584534</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2175,22 +2200,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2203,50 +2218,25 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123011004</v>
+        <v>123185939</v>
       </c>
       <c r="B13" t="n">
-        <v>57503</v>
+        <v>8447</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2255,53 +2245,54 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lövlunda, Lövlunda, Srm</t>
+          <t>Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566010</v>
+        <v>566060</v>
       </c>
       <c r="R13" t="n">
-        <v>6583585</v>
+        <v>6583553</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2325,22 +2316,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2351,31 +2342,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Äldre barrskogsmiljö</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2392,10 +2358,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123003959</v>
+        <v>123231344</v>
       </c>
       <c r="B14" t="n">
-        <v>57503</v>
+        <v>8447</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2404,37 +2370,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2444,10 +2407,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566582</v>
+        <v>566775</v>
       </c>
       <c r="R14" t="n">
-        <v>6584418</v>
+        <v>6584532</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2474,12 +2437,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2488,28 +2461,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emelie Bergermark</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123008919</v>
+        <v>123236226</v>
       </c>
       <c r="B15" t="n">
-        <v>8445</v>
+        <v>90955</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2522,46 +2496,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566404</v>
+        <v>566409</v>
       </c>
       <c r="R15" t="n">
-        <v>6584083</v>
+        <v>6583988</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2585,22 +2553,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2613,50 +2581,25 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123008823</v>
+        <v>123271947</v>
       </c>
       <c r="B16" t="n">
-        <v>5174</v>
+        <v>90990</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2665,54 +2608,44 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566444</v>
+        <v>566409</v>
       </c>
       <c r="R16" t="n">
-        <v>6583992</v>
+        <v>6583988</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2736,22 +2669,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2764,50 +2687,25 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123008173</v>
+        <v>123547348</v>
       </c>
       <c r="B17" t="n">
-        <v>8445</v>
+        <v>56722</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2820,46 +2718,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566354</v>
+        <v>566407</v>
       </c>
       <c r="R17" t="n">
-        <v>6584152</v>
+        <v>6584108</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2883,22 +2780,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2907,54 +2794,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123010595</v>
+        <v>123559251</v>
       </c>
       <c r="B18" t="n">
-        <v>8445</v>
+        <v>5176</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2967,21 +2828,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2996,17 +2857,17 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lövlunda, Lövlunda, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566008</v>
+        <v>566381</v>
       </c>
       <c r="R18" t="n">
-        <v>6583487</v>
+        <v>6584122</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3030,22 +2891,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3058,50 +2909,25 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123003070</v>
+        <v>123560721</v>
       </c>
       <c r="B19" t="n">
-        <v>56700</v>
+        <v>56722</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3146,13 +2972,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566462</v>
+        <v>566420</v>
       </c>
       <c r="R19" t="n">
-        <v>6584262</v>
+        <v>6584088</v>
       </c>
       <c r="S19" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3176,22 +3002,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:41</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:41</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3211,17 +3027,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anja Hynynen, Emelie Bergermark</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123050079</v>
+        <v>123607777</v>
       </c>
       <c r="B20" t="n">
-        <v>98502</v>
+        <v>57666</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3230,53 +3046,49 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566634</v>
+        <v>566358</v>
       </c>
       <c r="R20" t="n">
-        <v>6584453</v>
+        <v>6584063</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3300,22 +3112,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3330,22 +3132,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123034725</v>
+        <v>123607303</v>
       </c>
       <c r="B21" t="n">
-        <v>5176</v>
+        <v>8447</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3358,21 +3160,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3387,14 +3189,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Farfars trappa, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566550</v>
+        <v>566318</v>
       </c>
       <c r="R21" t="n">
-        <v>6584397</v>
+        <v>6584044</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3421,12 +3223,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3454,10 +3256,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123033899</v>
+        <v>123598850</v>
       </c>
       <c r="B22" t="n">
-        <v>5176</v>
+        <v>57529</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3466,47 +3268,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566802</v>
+        <v>566443</v>
       </c>
       <c r="R22" t="n">
-        <v>6584534</v>
+        <v>6584034</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3533,12 +3334,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3547,7 +3348,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3566,10 +3366,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123033108</v>
+        <v>123599090</v>
       </c>
       <c r="B23" t="n">
-        <v>97367</v>
+        <v>5176</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3582,38 +3382,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566666</v>
+        <v>566441</v>
       </c>
       <c r="R23" t="n">
-        <v>6584456</v>
+        <v>6583991</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3640,12 +3445,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3666,17 +3471,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Emelie Bergermark, Anja Hynynen</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123080289</v>
+        <v>123599223</v>
       </c>
       <c r="B24" t="n">
-        <v>98504</v>
+        <v>8436</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3685,45 +3490,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Öster om Höghäll, Slätthagen, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566632</v>
+        <v>566441</v>
       </c>
       <c r="R24" t="n">
-        <v>6584457</v>
+        <v>6583991</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3747,22 +3557,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3775,35 +3575,25 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Äldre barrskog.</t>
-        </is>
-      </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123077638</v>
+        <v>123607157</v>
       </c>
       <c r="B25" t="n">
-        <v>98504</v>
+        <v>91409</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3812,53 +3602,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Öster om Höghäll, Slätthagen, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566640</v>
+        <v>566318</v>
       </c>
       <c r="R25" t="n">
-        <v>6584477</v>
+        <v>6584044</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3882,27 +3658,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Växer längs den gamla kyrkstigen i äldre barrskog.</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3915,35 +3676,25 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Äldre barrskogsmiljö</t>
-        </is>
-      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123079585</v>
+        <v>123784683</v>
       </c>
       <c r="B26" t="n">
-        <v>98504</v>
+        <v>5196</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3952,50 +3703,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Öster om Höghäll, Slätthagen, Srm</t>
+          <t>Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566632</v>
+        <v>566011</v>
       </c>
       <c r="R26" t="n">
-        <v>6584462</v>
+        <v>6583560</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4022,27 +3770,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Växer i mossrik äldre barrskog.</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4055,35 +3788,25 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Äldre barrskog</t>
-        </is>
-      </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123080901</v>
+        <v>123783601</v>
       </c>
       <c r="B27" t="n">
-        <v>98504</v>
+        <v>90977</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4092,61 +3815,44 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Öster om Höghäll, Slätthagen, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566636</v>
+        <v>566212</v>
       </c>
       <c r="R27" t="n">
-        <v>6584458</v>
+        <v>6583882</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4170,27 +3876,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Knärot i äldre barrskog med vinterståndare.</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4203,72 +3894,65 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Äldre barrskog. Kontinuitetsskog</t>
-        </is>
-      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123241264</v>
+        <v>127060592</v>
       </c>
       <c r="B28" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98442</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4276,13 +3960,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566553</v>
+        <v>566759</v>
       </c>
       <c r="R28" t="n">
-        <v>6584351</v>
+        <v>6584518</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4306,12 +3990,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>21:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>21:38</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4338,62 +4032,51 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123232797</v>
+        <v>127055817</v>
       </c>
       <c r="B29" t="n">
-        <v>8436</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92607</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106554</v>
+        <v>4361</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566699</v>
+        <v>566433</v>
       </c>
       <c r="R29" t="n">
-        <v>6584476</v>
+        <v>6584038</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4417,22 +4100,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4441,7 +4124,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4460,63 +4142,52 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123185939</v>
+        <v>127058906</v>
       </c>
       <c r="B30" t="n">
-        <v>8447</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92607</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lövlunda, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566060</v>
+        <v>566330</v>
       </c>
       <c r="R30" t="n">
-        <v>6583553</v>
+        <v>6584106</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4543,22 +4214,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4585,15 +4256,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123231344</v>
+        <v>127056116</v>
       </c>
       <c r="B31" t="n">
         <v>8447</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4630,17 +4296,17 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566775</v>
+        <v>566376</v>
       </c>
       <c r="R31" t="n">
-        <v>6584532</v>
+        <v>6584044</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4664,22 +4330,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4688,7 +4354,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4707,42 +4372,46 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123236226</v>
+        <v>127057216</v>
       </c>
       <c r="B32" t="n">
-        <v>90955</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98442</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4750,13 +4419,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566409</v>
+        <v>566419</v>
       </c>
       <c r="R32" t="n">
-        <v>6583988</v>
+        <v>6583966</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4780,22 +4449,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4804,61 +4473,68 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123271947</v>
+        <v>127057091</v>
       </c>
       <c r="B33" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98442</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4866,13 +4542,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566409</v>
+        <v>566418</v>
       </c>
       <c r="R33" t="n">
-        <v>6583988</v>
+        <v>6583964</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4896,12 +4572,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Tre blommande knärot och i blåbärsriset ett tiotal plantor. Mellanskog planerar gallra i detta skogsbestånd.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4910,34 +4601,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123527972</v>
+        <v>127056859</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98442</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4962,32 +4647,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Morfars trappa, Morfars trappa, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566423</v>
+        <v>566415</v>
       </c>
       <c r="R34" t="n">
-        <v>6584223</v>
+        <v>6583965</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5011,12 +4692,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Mellanskog planerar gallra i skog med knärot.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5025,2411 +4721,21 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>123547348</v>
-      </c>
-      <c r="B35" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Morfars trappa, Srm</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>566407</v>
-      </c>
-      <c r="R35" t="n">
-        <v>6584108</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Kungsör</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Torpa</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>123559251</v>
-      </c>
-      <c r="B36" t="n">
-        <v>5176</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Morfars trappa, Srm</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>566381</v>
-      </c>
-      <c r="R36" t="n">
-        <v>6584122</v>
-      </c>
-      <c r="S36" t="n">
-        <v>10</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Kungsör</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Torpa</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>123560721</v>
-      </c>
-      <c r="B37" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Morfars trappa, Srm</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>566420</v>
-      </c>
-      <c r="R37" t="n">
-        <v>6584088</v>
-      </c>
-      <c r="S37" t="n">
-        <v>10</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Kungsör</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Torpa</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>123607777</v>
-      </c>
-      <c r="B38" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Morfars trappa, Srm</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>566358</v>
-      </c>
-      <c r="R38" t="n">
-        <v>6584063</v>
-      </c>
-      <c r="S38" t="n">
-        <v>25</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Kungsör</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Torpa</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>123607303</v>
-      </c>
-      <c r="B39" t="n">
-        <v>8447</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>106545</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Tomicus minor</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Morfars trappa, Srm</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>566318</v>
-      </c>
-      <c r="R39" t="n">
-        <v>6584044</v>
-      </c>
-      <c r="S39" t="n">
-        <v>10</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Kungsör</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Torpa</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>123598850</v>
-      </c>
-      <c r="B40" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Morfars trappa, Srm</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>566443</v>
-      </c>
-      <c r="R40" t="n">
-        <v>6584034</v>
-      </c>
-      <c r="S40" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Kungsör</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Torpa</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>123599090</v>
-      </c>
-      <c r="B41" t="n">
-        <v>5176</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Morfars trappa, Srm</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>566441</v>
-      </c>
-      <c r="R41" t="n">
-        <v>6583991</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Kungsör</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Torpa</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>123599223</v>
-      </c>
-      <c r="B42" t="n">
-        <v>8436</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>106554</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Björksplintborre</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Scolytus ratzeburgii</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Morfars trappa, Srm</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>566441</v>
-      </c>
-      <c r="R42" t="n">
-        <v>6583991</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Kungsör</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Torpa</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="inlineStr"/>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>123607157</v>
-      </c>
-      <c r="B43" t="n">
-        <v>91409</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>6040162</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Leptoporus erubescens</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Morfars trappa, Srm</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>566318</v>
-      </c>
-      <c r="R43" t="n">
-        <v>6584044</v>
-      </c>
-      <c r="S43" t="n">
-        <v>10</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Kungsör</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Torpa</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="inlineStr"/>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>123784683</v>
-      </c>
-      <c r="B44" t="n">
-        <v>5196</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>105930</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Semanotus undatus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Lövlunda, Srm</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>566011</v>
-      </c>
-      <c r="R44" t="n">
-        <v>6583560</v>
-      </c>
-      <c r="S44" t="n">
-        <v>10</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Kungsör</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Torpa</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2025-04-05</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2025-04-05</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF44" t="inlineStr"/>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>123790035</v>
-      </c>
-      <c r="B45" t="n">
-        <v>56471</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>208255</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Skogsödla</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Zootoca vivipara</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Hällarna vid kraftledningsgatan, Srm</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>566426</v>
-      </c>
-      <c r="R45" t="n">
-        <v>6584234</v>
-      </c>
-      <c r="S45" t="n">
-        <v>25</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Kungsör</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Torpa</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2025-04-05</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2025-04-05</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="inlineStr"/>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Emelie Bergermark</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Emelie Bergermark</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>123783535</v>
-      </c>
-      <c r="B46" t="n">
-        <v>5176</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Björnsten, Srm</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>566702</v>
-      </c>
-      <c r="R46" t="n">
-        <v>6584466</v>
-      </c>
-      <c r="S46" t="n">
-        <v>10</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Kungsör</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Torpa</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2025-04-05</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2025-04-05</t>
-        </is>
-      </c>
-      <c r="AD46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>123783601</v>
-      </c>
-      <c r="B47" t="n">
-        <v>90977</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Morfars trappa, Srm</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>566212</v>
-      </c>
-      <c r="R47" t="n">
-        <v>6583882</v>
-      </c>
-      <c r="S47" t="n">
-        <v>10</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Kungsör</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Torpa</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2025-04-05</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2025-04-05</t>
-        </is>
-      </c>
-      <c r="AD47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF47" t="inlineStr"/>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>127061455</v>
-      </c>
-      <c r="B48" t="n">
-        <v>57459</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>102118</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Nattskärra</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Caprimulgus europaeus</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Morfars trappa, Srm</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>566436</v>
-      </c>
-      <c r="R48" t="n">
-        <v>6584241</v>
-      </c>
-      <c r="S48" t="n">
-        <v>21</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Kungsör</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Torpa</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>22:16</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>22:16</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Nattskärra vid hällmarken.</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>127060592</v>
-      </c>
-      <c r="B49" t="n">
-        <v>98436</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Björnsten, Srm</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>566759</v>
-      </c>
-      <c r="R49" t="n">
-        <v>6584518</v>
-      </c>
-      <c r="S49" t="n">
-        <v>16</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Kungsör</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Torpa</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>21:37</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>21:38</t>
-        </is>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>127055817</v>
-      </c>
-      <c r="B50" t="n">
-        <v>92601</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>4361</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Orange taggsvamp</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Hydnellum aurantiacum</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Morfars trappa, Srm</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>566433</v>
-      </c>
-      <c r="R50" t="n">
-        <v>6584038</v>
-      </c>
-      <c r="S50" t="n">
-        <v>9</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Kungsör</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Torpa</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>18:13</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>18:13</t>
-        </is>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>127056116</v>
-      </c>
-      <c r="B51" t="n">
-        <v>8447</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>106545</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Tomicus minor</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Morfars trappa, Srm</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>566376</v>
-      </c>
-      <c r="R51" t="n">
-        <v>6584044</v>
-      </c>
-      <c r="S51" t="n">
-        <v>15</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Kungsör</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Torpa</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>18:27</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>18:27</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>127058906</v>
-      </c>
-      <c r="B52" t="n">
-        <v>92601</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>4361</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Orange taggsvamp</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Hydnellum aurantiacum</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Morfars trappa, Srm</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>566330</v>
-      </c>
-      <c r="R52" t="n">
-        <v>6584106</v>
-      </c>
-      <c r="S52" t="n">
-        <v>4</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Kungsör</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Torpa</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>20:32</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>20:32</t>
-        </is>
-      </c>
-      <c r="AD52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>127057216</v>
-      </c>
-      <c r="B53" t="n">
-        <v>98436</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Morfars trappa, Srm</t>
-        </is>
-      </c>
-      <c r="Q53" t="n">
-        <v>566419</v>
-      </c>
-      <c r="R53" t="n">
-        <v>6583966</v>
-      </c>
-      <c r="S53" t="n">
-        <v>4</v>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Kungsör</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>Torpa</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>19:21</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>19:21</t>
-        </is>
-      </c>
-      <c r="AD53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AW53" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>127057091</v>
-      </c>
-      <c r="B54" t="n">
-        <v>98436</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Morfars trappa, Srm</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>566418</v>
-      </c>
-      <c r="R54" t="n">
-        <v>6583964</v>
-      </c>
-      <c r="S54" t="n">
-        <v>4</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Kungsör</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Torpa</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Tre blommande knärot och i blåbärsriset ett tiotal plantor. Mellanskog planerar gallra i detta skogsbestånd.</t>
-        </is>
-      </c>
-      <c r="AD54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>127056859</v>
-      </c>
-      <c r="B55" t="n">
-        <v>98436</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Morfars trappa, Srm</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>566415</v>
-      </c>
-      <c r="R55" t="n">
-        <v>6583965</v>
-      </c>
-      <c r="S55" t="n">
-        <v>4</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Kungsör</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Torpa</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>19:03</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>19:03</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Mellanskog planerar gallra i skog med knärot.</t>
-        </is>
-      </c>
-      <c r="AD55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4142,41 +4142,43 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127058906</v>
+        <v>127056116</v>
       </c>
       <c r="B30" t="n">
-        <v>92607</v>
+        <v>8447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4184,13 +4186,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566330</v>
+        <v>566376</v>
       </c>
       <c r="R30" t="n">
-        <v>6584106</v>
+        <v>6584044</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4219,7 +4221,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4229,7 +4231,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4244,55 +4246,53 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127056116</v>
+        <v>127058906</v>
       </c>
       <c r="B31" t="n">
-        <v>8447</v>
+        <v>92607</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>4361</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4300,13 +4300,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566376</v>
+        <v>566330</v>
       </c>
       <c r="R31" t="n">
-        <v>6584044</v>
+        <v>6584106</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4360,12 +4360,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4142,43 +4142,41 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127056116</v>
+        <v>127058906</v>
       </c>
       <c r="B30" t="n">
-        <v>8447</v>
+        <v>92607</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4186,13 +4184,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566376</v>
+        <v>566330</v>
       </c>
       <c r="R30" t="n">
-        <v>6584044</v>
+        <v>6584106</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4221,7 +4219,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4231,7 +4229,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4246,53 +4244,55 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127058906</v>
+        <v>127056116</v>
       </c>
       <c r="B31" t="n">
-        <v>92607</v>
+        <v>8447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4361</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4300,13 +4300,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566330</v>
+        <v>566376</v>
       </c>
       <c r="R31" t="n">
-        <v>6584106</v>
+        <v>6584044</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4360,12 +4360,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -3912,7 +3912,7 @@
         <v>127060592</v>
       </c>
       <c r="B28" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>127055817</v>
       </c>
       <c r="B29" t="n">
-        <v>92607</v>
+        <v>92608</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>127058906</v>
       </c>
       <c r="B30" t="n">
-        <v>92607</v>
+        <v>92608</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>127057216</v>
       </c>
       <c r="B32" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>127057091</v>
       </c>
       <c r="B33" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>127056859</v>
       </c>
       <c r="B34" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -3912,7 +3912,7 @@
         <v>127060592</v>
       </c>
       <c r="B28" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>127055817</v>
       </c>
       <c r="B29" t="n">
-        <v>92608</v>
+        <v>92612</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>127058906</v>
       </c>
       <c r="B30" t="n">
-        <v>92608</v>
+        <v>92612</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>127056116</v>
       </c>
       <c r="B31" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>127057216</v>
       </c>
       <c r="B32" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>127057091</v>
       </c>
       <c r="B33" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>127056859</v>
       </c>
       <c r="B34" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -3912,7 +3912,7 @@
         <v>127060592</v>
       </c>
       <c r="B28" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>127057216</v>
       </c>
       <c r="B32" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>127057091</v>
       </c>
       <c r="B33" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>127056859</v>
       </c>
       <c r="B34" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -3912,7 +3912,7 @@
         <v>127060592</v>
       </c>
       <c r="B28" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>127055817</v>
       </c>
       <c r="B29" t="n">
-        <v>92612</v>
+        <v>92614</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>127058906</v>
       </c>
       <c r="B30" t="n">
-        <v>92612</v>
+        <v>92614</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>127057216</v>
       </c>
       <c r="B32" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>127057091</v>
       </c>
       <c r="B33" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>127056859</v>
       </c>
       <c r="B34" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -3912,7 +3912,7 @@
         <v>127060592</v>
       </c>
       <c r="B28" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>127055817</v>
       </c>
       <c r="B29" t="n">
-        <v>92614</v>
+        <v>92620</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4142,41 +4142,43 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127058906</v>
+        <v>127056116</v>
       </c>
       <c r="B30" t="n">
-        <v>92614</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4184,13 +4186,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566330</v>
+        <v>566376</v>
       </c>
       <c r="R30" t="n">
-        <v>6584106</v>
+        <v>6584044</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4219,7 +4221,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4229,7 +4231,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4244,55 +4246,53 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127056116</v>
+        <v>127058906</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>92620</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>4361</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4300,13 +4300,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566376</v>
+        <v>566330</v>
       </c>
       <c r="R31" t="n">
-        <v>6584044</v>
+        <v>6584106</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4360,12 +4360,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4375,7 +4375,7 @@
         <v>127057216</v>
       </c>
       <c r="B32" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>127057091</v>
       </c>
       <c r="B33" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>127056859</v>
       </c>
       <c r="B34" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4737,6 +4737,564 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128647065</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91678</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1101</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Gropticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Postia guttulata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Morfars trappa, Srm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>566381</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6583987</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128647344</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58055</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Morfars trappa, Srm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>566340</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6584048</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128638281</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98572</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Morfars trappa (knärot 4), Srm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>566418</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6583966</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>U-Kun-0131</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>X: (5), 2 pl, A: 693/440(5), minst 13 pl, B: 690/441 (5) not dvs minst 2 pl, foton OK. Mellanskog planerad gallring</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128647617</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91678</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1101</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Gropticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Postia guttulata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Morfars trappa, Srm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>566352</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6584096</v>
+      </c>
+      <c r="S38" t="n">
+        <v>6</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128637642</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98572</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Björnsten (knärot 4), Srm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>566758</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6584518</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>foto (egentligen (16))</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91678</v>
+        <v>91683</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>128647344</v>
       </c>
       <c r="B36" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4945,64 +4945,51 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128638281</v>
+        <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>98572</v>
+        <v>91683</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>1101</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Morfars trappa (knärot 4), Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>566418</v>
+        <v>566352</v>
       </c>
       <c r="R37" t="n">
-        <v>6583966</v>
+        <v>6584096</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5024,24 +5011,14 @@
           <t>Torpa</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>U-Kun-0131</t>
-        </is>
-      </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>X: (5), 2 pl, A: 693/440(5), minst 13 pl, B: 690/441 (5) not dvs minst 2 pl, foton OK. Mellanskog planerad gallring</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5057,67 +5034,76 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128647617</v>
+        <v>128637642</v>
       </c>
       <c r="B38" t="n">
-        <v>91678</v>
+        <v>98579</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1101</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Morfars trappa, Srm</t>
+          <t>Björnsten (knärot 4), Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566352</v>
+        <v>566758</v>
       </c>
       <c r="R38" t="n">
-        <v>6584096</v>
+        <v>6584518</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5139,14 +5125,24 @@
           <t>Torpa</t>
         </is>
       </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>U-Kun-0129</t>
+        </is>
+      </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>foto (egentligen (16))</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5162,134 +5158,15 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
           <t>Anja Hynynen</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>128637642</v>
-      </c>
-      <c r="B39" t="n">
-        <v>98572</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Björnsten (knärot 4), Srm</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>566758</v>
-      </c>
-      <c r="R39" t="n">
-        <v>6584518</v>
-      </c>
-      <c r="S39" t="n">
-        <v>25</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Kungsör</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Torpa</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>foto (egentligen (16))</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Bo Eriksson</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
+      <c r="AY38" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91683</v>
+        <v>91689</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91683</v>
+        <v>91689</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>128637642</v>
       </c>
       <c r="B38" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91689</v>
+        <v>91691</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91689</v>
+        <v>91691</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>128637642</v>
       </c>
       <c r="B38" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -5049,7 +5049,7 @@
         <v>128637642</v>
       </c>
       <c r="B38" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91691</v>
+        <v>91692</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91691</v>
+        <v>91692</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>128637642</v>
       </c>
       <c r="B38" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91692</v>
+        <v>91719</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>128647344</v>
       </c>
       <c r="B36" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91692</v>
+        <v>91719</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>128637642</v>
       </c>
       <c r="B38" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91719</v>
+        <v>91724</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91719</v>
+        <v>91724</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>128637642</v>
       </c>
       <c r="B38" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91724</v>
+        <v>91729</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91724</v>
+        <v>91729</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>128637642</v>
       </c>
       <c r="B38" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91729</v>
+        <v>91733</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>128647344</v>
       </c>
       <c r="B36" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91729</v>
+        <v>91733</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>128637642</v>
       </c>
       <c r="B38" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91733</v>
+        <v>91738</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>128647344</v>
       </c>
       <c r="B36" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91733</v>
+        <v>91738</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>128637642</v>
       </c>
       <c r="B38" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91740</v>
+        <v>91745</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91740</v>
+        <v>91745</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>128637642</v>
       </c>
       <c r="B38" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91745</v>
+        <v>91751</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91745</v>
+        <v>91751</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>128637642</v>
       </c>
       <c r="B38" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91751</v>
+        <v>91758</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>128647344</v>
       </c>
       <c r="B36" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91751</v>
+        <v>91758</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>128637642</v>
       </c>
       <c r="B38" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4948,7 +4948,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91758</v>
+        <v>91765</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4948,7 +4948,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91765</v>
+        <v>91767</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91758</v>
+        <v>91768</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91768</v>
+        <v>91776</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91767</v>
+        <v>91776</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91776</v>
+        <v>91777</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91776</v>
+        <v>91777</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91777</v>
+        <v>91780</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91777</v>
+        <v>91780</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91780</v>
+        <v>91782</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91780</v>
+        <v>91782</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91782</v>
+        <v>91786</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91782</v>
+        <v>91786</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91786</v>
+        <v>91787</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91786</v>
+        <v>91787</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91787</v>
+        <v>91790</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91787</v>
+        <v>91790</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4815,6 +4815,11 @@
           <t>2025-09-23</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Vid gran.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -5021,6 +5026,11 @@
           <t>2025-09-23</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Vid gran.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91790</v>
+        <v>91818</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91790</v>
+        <v>91818</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91818</v>
+        <v>91824</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91818</v>
+        <v>91824</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91824</v>
+        <v>91825</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91824</v>
+        <v>91825</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5182,6 +5182,102 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127056507</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92007</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Morfars trappa, Srm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>566351</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6584071</v>
+      </c>
+      <c r="S39" t="n">
+        <v>11</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91825</v>
+        <v>91830</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91825</v>
+        <v>91830</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>127056507</v>
       </c>
       <c r="B39" t="n">
-        <v>92007</v>
+        <v>92012</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91830</v>
+        <v>91834</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91830</v>
+        <v>91834</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>127056507</v>
       </c>
       <c r="B39" t="n">
-        <v>92012</v>
+        <v>92016</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>127056507</v>
       </c>
       <c r="B39" t="n">
-        <v>92016</v>
+        <v>92018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -5187,7 +5187,7 @@
         <v>127056507</v>
       </c>
       <c r="B39" t="n">
-        <v>92018</v>
+        <v>92021</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5196,6 +5196,11 @@
       </c>
       <c r="E39" t="n">
         <v>6040186</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91836</v>
+        <v>91839</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91836</v>
+        <v>91839</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91839</v>
+        <v>91842</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91839</v>
+        <v>91842</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>127056507</v>
       </c>
       <c r="B39" t="n">
-        <v>92021</v>
+        <v>92024</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -4742,7 +4742,7 @@
         <v>128647065</v>
       </c>
       <c r="B35" t="n">
-        <v>91842</v>
+        <v>91843</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>128647617</v>
       </c>
       <c r="B37" t="n">
-        <v>91842</v>
+        <v>91843</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>127056507</v>
       </c>
       <c r="B39" t="n">
-        <v>92024</v>
+        <v>92025</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -5187,7 +5187,7 @@
         <v>127056507</v>
       </c>
       <c r="B39" t="n">
-        <v>92025</v>
+        <v>92042</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -3912,7 +3912,7 @@
         <v>127060592</v>
       </c>
       <c r="B28" t="n">
-        <v>98456</v>
+        <v>98436</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>127055817</v>
       </c>
       <c r="B29" t="n">
-        <v>92620</v>
+        <v>92601</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>127056116</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>8447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>127058906</v>
       </c>
       <c r="B31" t="n">
-        <v>92620</v>
+        <v>92601</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>127057216</v>
       </c>
       <c r="B32" t="n">
-        <v>98456</v>
+        <v>98436</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>127057091</v>
       </c>
       <c r="B33" t="n">
-        <v>98456</v>
+        <v>98436</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>127056859</v>
       </c>
       <c r="B34" t="n">
-        <v>98456</v>
+        <v>98436</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -3912,7 +3912,7 @@
         <v>127060592</v>
       </c>
       <c r="B28" t="n">
-        <v>98436</v>
+        <v>98456</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>127055817</v>
       </c>
       <c r="B29" t="n">
-        <v>92601</v>
+        <v>92620</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>127056116</v>
       </c>
       <c r="B30" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>127058906</v>
       </c>
       <c r="B31" t="n">
-        <v>92601</v>
+        <v>92620</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>127057216</v>
       </c>
       <c r="B32" t="n">
-        <v>98436</v>
+        <v>98456</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>127057091</v>
       </c>
       <c r="B33" t="n">
-        <v>98436</v>
+        <v>98456</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>127056859</v>
       </c>
       <c r="B34" t="n">
-        <v>98436</v>
+        <v>98456</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>122924806</v>
       </c>
       <c r="B2" t="n">
-        <v>56697</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -812,12 +807,7 @@
         <v>122924906</v>
       </c>
       <c r="B3" t="n">
-        <v>56697</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57053</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -951,12 +941,7 @@
         <v>122925010</v>
       </c>
       <c r="B4" t="n">
-        <v>56697</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57053</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2705,12 +2690,7 @@
         <v>123547348</v>
       </c>
       <c r="B17" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57053</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2927,12 +2907,7 @@
         <v>123560721</v>
       </c>
       <c r="B19" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57053</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122924806</v>
+        <v>128647065</v>
       </c>
       <c r="B2" t="n">
-        <v>57073</v>
+        <v>92147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>1101</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566416</v>
+        <v>566381</v>
       </c>
       <c r="R2" t="n">
-        <v>6584024</v>
+        <v>6583987</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,22 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Vid gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,88 +762,70 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Hällmarksskog.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122924906</v>
+        <v>128647617</v>
       </c>
       <c r="B3" t="n">
-        <v>57073</v>
+        <v>92147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>1101</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566411</v>
+        <v>566352</v>
       </c>
       <c r="R3" t="n">
-        <v>6584027</v>
+        <v>6584096</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,27 +849,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>spillning i äldre hälimarksskog. Skogen är avverkningsanmäld.</t>
+          <t>Vid gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,88 +868,70 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Hällmarksskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122925010</v>
+        <v>123271947</v>
       </c>
       <c r="B4" t="n">
-        <v>57073</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566430</v>
+        <v>566409</v>
       </c>
       <c r="R4" t="n">
-        <v>6584038</v>
+        <v>6583988</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1015,27 +955,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spillning i äldre hällmarksskog. Skogen är avverkningsanmäld.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,43 +969,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Hällmarksskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123009148</v>
+        <v>127055817</v>
       </c>
       <c r="B5" t="n">
-        <v>79399</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,44 +999,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566372</v>
+        <v>566433</v>
       </c>
       <c r="R5" t="n">
-        <v>6584091</v>
+        <v>6584038</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1149,27 +1056,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Substrat är gammal tallstubbe i hällmark.</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,110 +1080,73 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123009266</v>
+        <v>127058906</v>
       </c>
       <c r="B6" t="n">
-        <v>8445</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566408</v>
+        <v>566330</v>
       </c>
       <c r="R6" t="n">
-        <v>6584004</v>
+        <v>6584106</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1305,22 +1170,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1329,34 +1194,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Hälmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1373,65 +1212,51 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123008304</v>
+        <v>123236226</v>
       </c>
       <c r="B7" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Söder om Höghäll, Lövlunda, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566374</v>
+        <v>566409</v>
       </c>
       <c r="R7" t="n">
-        <v>6584013</v>
+        <v>6583988</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1455,27 +1280,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska hackmärken på stående död tall.</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1484,93 +1304,70 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Hällmarksskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123011004</v>
+        <v>123783601</v>
       </c>
       <c r="B8" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lövlunda, Lövlunda, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566010</v>
+        <v>566212</v>
       </c>
       <c r="R8" t="n">
-        <v>6583585</v>
+        <v>6583882</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1594,22 +1391,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1618,89 +1405,58 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Äldre barrskogsmiljö</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123008919</v>
+        <v>123009148</v>
       </c>
       <c r="B9" t="n">
-        <v>8445</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1710,10 +1466,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566404</v>
+        <v>566372</v>
       </c>
       <c r="R9" t="n">
-        <v>6584083</v>
+        <v>6584091</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1756,6 +1512,11 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Substrat är gammal tallstubbe i hällmark.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1808,15 +1569,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123008823</v>
+        <v>123008304</v>
       </c>
       <c r="B10" t="n">
-        <v>5174</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1824,30 +1580,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1861,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566444</v>
+        <v>566374</v>
       </c>
       <c r="R10" t="n">
-        <v>6583992</v>
+        <v>6584013</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1909,13 +1664,17 @@
           <t>13:00</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på stående död tall.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1927,21 +1686,6 @@
       <c r="AI10" t="inlineStr">
         <is>
           <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1959,15 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123010595</v>
+        <v>123011004</v>
       </c>
       <c r="B11" t="n">
-        <v>8445</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1975,43 +1714,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lövlunda, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566008</v>
+        <v>566010</v>
       </c>
       <c r="R11" t="n">
-        <v>6583487</v>
+        <v>6583585</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2043,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2053,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2062,7 +1804,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2073,22 +1814,22 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Äldre barrskogsmiljö</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2106,15 +1847,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123033899</v>
+        <v>123598850</v>
       </c>
       <c r="B12" t="n">
-        <v>5176</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2122,43 +1858,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566802</v>
+        <v>566443</v>
       </c>
       <c r="R12" t="n">
-        <v>6584534</v>
+        <v>6584034</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2185,12 +1920,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2199,7 +1934,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2218,15 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123185939</v>
+        <v>122924806</v>
       </c>
       <c r="B13" t="n">
-        <v>8447</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2234,50 +1963,49 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lövlunda, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566060</v>
+        <v>566416</v>
       </c>
       <c r="R13" t="n">
-        <v>6583553</v>
+        <v>6584024</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2301,22 +2029,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2327,6 +2055,16 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Hällmarksskog.</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2343,15 +2081,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123231344</v>
+        <v>122924906</v>
       </c>
       <c r="B14" t="n">
-        <v>8447</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2359,46 +2092,49 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566775</v>
+        <v>566411</v>
       </c>
       <c r="R14" t="n">
-        <v>6584532</v>
+        <v>6584027</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2422,22 +2158,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>spillning i äldre hälimarksskog. Skogen är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2446,34 +2187,38 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123236226</v>
+        <v>122925010</v>
       </c>
       <c r="B15" t="n">
-        <v>90955</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2481,40 +2226,49 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Morfars trappa, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566409</v>
+        <v>566430</v>
       </c>
       <c r="R15" t="n">
-        <v>6583988</v>
+        <v>6584038</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2538,22 +2292,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Spillning i äldre hällmarksskog. Skogen är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2562,61 +2321,70 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123271947</v>
+        <v>123547348</v>
       </c>
       <c r="B16" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2624,10 +2392,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566409</v>
+        <v>566407</v>
       </c>
       <c r="R16" t="n">
-        <v>6583988</v>
+        <v>6584108</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2654,12 +2422,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2668,7 +2436,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2687,10 +2454,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123547348</v>
+        <v>123560721</v>
       </c>
       <c r="B17" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2730,10 +2497,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566407</v>
+        <v>566420</v>
       </c>
       <c r="R17" t="n">
-        <v>6584108</v>
+        <v>6584088</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2792,15 +2559,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123559251</v>
+        <v>123008823</v>
       </c>
       <c r="B18" t="n">
-        <v>5176</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2831,23 +2593,27 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Morfars trappa, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566381</v>
+        <v>566444</v>
       </c>
       <c r="R18" t="n">
-        <v>6584122</v>
+        <v>6583992</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2871,12 +2637,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2889,25 +2665,50 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123560721</v>
+        <v>123033899</v>
       </c>
       <c r="B19" t="n">
-        <v>57073</v>
+        <v>5179</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2915,42 +2716,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Morfars trappa, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566420</v>
+        <v>566802</v>
       </c>
       <c r="R19" t="n">
-        <v>6584088</v>
+        <v>6584534</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2977,12 +2779,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2991,6 +2793,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3009,45 +2812,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123607777</v>
+        <v>123559251</v>
       </c>
       <c r="B20" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3057,13 +2856,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566358</v>
+        <v>566381</v>
       </c>
       <c r="R20" t="n">
-        <v>6584063</v>
+        <v>6584122</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3101,6 +2900,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3119,15 +2919,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123607303</v>
+        <v>123599090</v>
       </c>
       <c r="B21" t="n">
-        <v>8447</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3135,21 +2930,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3168,10 +2963,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566318</v>
+        <v>566441</v>
       </c>
       <c r="R21" t="n">
-        <v>6584044</v>
+        <v>6583991</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3231,58 +3026,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123598850</v>
+        <v>123783535</v>
       </c>
       <c r="B22" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Morfars trappa, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566443</v>
+        <v>566702</v>
       </c>
       <c r="R22" t="n">
-        <v>6584034</v>
+        <v>6584466</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3309,12 +3100,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3323,6 +3114,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3341,15 +3133,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123599090</v>
+        <v>128647344</v>
       </c>
       <c r="B23" t="n">
-        <v>5176</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3357,30 +3144,29 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3390,10 +3176,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566441</v>
+        <v>566340</v>
       </c>
       <c r="R23" t="n">
-        <v>6583991</v>
+        <v>6584048</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3420,12 +3206,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3434,7 +3220,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3453,46 +3238,40 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123599223</v>
+        <v>123607777</v>
       </c>
       <c r="B24" t="n">
-        <v>8436</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3502,13 +3281,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566441</v>
+        <v>566358</v>
       </c>
       <c r="R24" t="n">
-        <v>6583991</v>
+        <v>6584063</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3546,7 +3325,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3565,48 +3343,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123607157</v>
+        <v>123784683</v>
       </c>
       <c r="B25" t="n">
-        <v>91409</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6040162</v>
+        <v>105930</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Morfars trappa, Srm</t>
+          <t>Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566318</v>
+        <v>566011</v>
       </c>
       <c r="R25" t="n">
-        <v>6584044</v>
+        <v>6583560</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3633,12 +3417,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3666,15 +3450,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123784683</v>
+        <v>123008173</v>
       </c>
       <c r="B26" t="n">
-        <v>5196</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3682,21 +3461,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3711,17 +3490,17 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lövlunda, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566011</v>
+        <v>566354</v>
       </c>
       <c r="R26" t="n">
-        <v>6583560</v>
+        <v>6584152</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3745,12 +3524,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3763,30 +3552,50 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123783601</v>
+        <v>123008919</v>
       </c>
       <c r="B27" t="n">
-        <v>90977</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3794,40 +3603,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Morfars trappa, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566212</v>
+        <v>566404</v>
       </c>
       <c r="R27" t="n">
-        <v>6583882</v>
+        <v>6584083</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3851,12 +3666,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3869,79 +3694,101 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127060592</v>
+        <v>123009266</v>
       </c>
       <c r="B28" t="n">
-        <v>98456</v>
+        <v>8455</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Björnsten, Srm</t>
+          <t>Söder om Höghäll, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566759</v>
+        <v>566408</v>
       </c>
       <c r="R28" t="n">
-        <v>6584518</v>
+        <v>6584004</v>
       </c>
       <c r="S28" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3965,22 +3812,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>21:37</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>21:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3989,69 +3836,101 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Hälmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127055817</v>
+        <v>123010595</v>
       </c>
       <c r="B29" t="n">
-        <v>92620</v>
+        <v>8455</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4361</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Morfars trappa, Srm</t>
+          <t>Lövlunda, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566433</v>
+        <v>566008</v>
       </c>
       <c r="R29" t="n">
-        <v>6584038</v>
+        <v>6583487</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4075,22 +3954,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4099,28 +3978,54 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127056116</v>
+        <v>123185939</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4145,7 +4050,11 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -4157,17 +4066,17 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Morfars trappa, Srm</t>
+          <t>Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566376</v>
+        <v>566060</v>
       </c>
       <c r="R30" t="n">
-        <v>6584044</v>
+        <v>6583553</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4191,22 +4100,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4221,67 +4130,69 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127058906</v>
+        <v>123231344</v>
       </c>
       <c r="B31" t="n">
-        <v>92620</v>
+        <v>8455</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4361</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Morfars trappa, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566330</v>
+        <v>566775</v>
       </c>
       <c r="R31" t="n">
-        <v>6584106</v>
+        <v>6584532</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4305,22 +4216,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4329,64 +4240,62 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127057216</v>
+        <v>123607303</v>
       </c>
       <c r="B32" t="n">
-        <v>98456</v>
+        <v>8455</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4394,13 +4303,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566419</v>
+        <v>566318</v>
       </c>
       <c r="R32" t="n">
-        <v>6583966</v>
+        <v>6584044</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4424,22 +4333,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>19:21</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>19:21</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4448,68 +4347,62 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127057091</v>
+        <v>127056116</v>
       </c>
       <c r="B33" t="n">
-        <v>98456</v>
+        <v>8455</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4517,13 +4410,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566418</v>
+        <v>566376</v>
       </c>
       <c r="R33" t="n">
-        <v>6583964</v>
+        <v>6584044</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4552,7 +4445,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4562,12 +4455,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Tre blommande knärot och i blåbärsriset ett tiotal plantor. Mellanskog planerar gallra i detta skogsbestånd.</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4582,68 +4470,73 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127056859</v>
+        <v>122924019</v>
       </c>
       <c r="B34" t="n">
-        <v>98456</v>
+        <v>8444</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Morfars trappa, Srm</t>
+          <t>Slogan, Lövlunda, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566415</v>
+        <v>565940</v>
       </c>
       <c r="R34" t="n">
-        <v>6583965</v>
+        <v>6583526</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4667,27 +4560,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>19:03</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Mellanskog planerar gallra i skog med knärot.</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4696,8 +4584,19 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Fuktig skogsmiljö med blandade trädslag.</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4714,48 +4613,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128647065</v>
+        <v>123232797</v>
       </c>
       <c r="B35" t="n">
-        <v>91843</v>
+        <v>8444</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1101</v>
+        <v>106554</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Morfars trappa, Srm</t>
+          <t>Björnsten, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566381</v>
+        <v>566699</v>
       </c>
       <c r="R35" t="n">
-        <v>6583987</v>
+        <v>6584476</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4782,17 +4687,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Vid gran.</t>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4820,10 +4730,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128647344</v>
+        <v>123599223</v>
       </c>
       <c r="B36" t="n">
-        <v>58095</v>
+        <v>8444</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4831,29 +4741,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103015</v>
+        <v>106554</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4863,10 +4774,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566340</v>
+        <v>566441</v>
       </c>
       <c r="R36" t="n">
-        <v>6584048</v>
+        <v>6583991</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4893,12 +4804,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4907,6 +4818,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4925,37 +4837,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128647617</v>
+        <v>127056859</v>
       </c>
       <c r="B37" t="n">
-        <v>91843</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1101</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4963,13 +4880,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>566352</v>
+        <v>566415</v>
       </c>
       <c r="R37" t="n">
-        <v>6584096</v>
+        <v>6583965</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4993,17 +4910,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Vid gran.</t>
+          <t>Mellanskog planerar gallra i skog med knärot.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5012,29 +4939,28 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128637642</v>
+        <v>127057091</v>
       </c>
       <c r="B38" t="n">
-        <v>98669</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5061,7 +4987,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5078,17 +5004,17 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Björnsten (knärot 4), Srm</t>
+          <t>Morfars trappa, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566758</v>
+        <v>566418</v>
       </c>
       <c r="R38" t="n">
-        <v>6584518</v>
+        <v>6583964</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5110,24 +5036,29 @@
           <t>Torpa</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>U-Kun-0129</t>
-        </is>
-      </c>
       <c r="Y38" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>foto (egentligen (16))</t>
+          <t>Tre blommande knärot och i blåbärsriset ett tiotal plantor. Mellanskog planerar gallra i detta skogsbestånd.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5136,60 +5067,64 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127056507</v>
+        <v>127057216</v>
       </c>
       <c r="B39" t="n">
-        <v>92058</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6040186</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5197,13 +5132,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566351</v>
+        <v>566419</v>
       </c>
       <c r="R39" t="n">
-        <v>6584071</v>
+        <v>6583966</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5230,33 +5165,748 @@
           <t>2025-07-31</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127058829</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Morfars trappa, Lövlunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>566334</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6584135</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Fyra blommande knärot. 16 plantor intill hällmarken.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127060592</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Björnsten, Srm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>566759</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6584518</v>
+      </c>
+      <c r="S41" t="n">
+        <v>16</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>21:37</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>21:38</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
           <t>Anja Hynynen</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
+      <c r="AX41" t="inlineStr">
         <is>
           <t>Anja Hynynen</t>
         </is>
       </c>
-      <c r="AY39" t="inlineStr"/>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128637642</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Björnsten (knärot1), Srm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>566758</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6584518</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>U-Kun-0129</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>foto (egentligen (16))</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128637852</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Morfars trappa (knärot3), Srm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>566335</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6584136</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>U-Kun-0130</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>4 på i blom, foto</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>123607157</v>
+      </c>
+      <c r="B44" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Morfars trappa, Srm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>566318</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6584044</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127056507</v>
+      </c>
+      <c r="B45" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Morfars trappa, Srm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>566351</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6584071</v>
+      </c>
+      <c r="S45" t="n">
+        <v>11</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9320-2025 artfynd.xlsx
+++ b/artfynd/A 9320-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128647065</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128647617</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123271947</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127055817</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1209,6 +1234,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127058906</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1320,6 +1350,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123236226</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123783601</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1566,6 +1606,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123009148</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1700,6 +1745,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123008304</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1844,6 +1894,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123011004</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1949,6 +2004,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123598850</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2078,6 +2138,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122924806</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2212,6 +2277,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122924906</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2346,6 +2416,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122925010</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2451,6 +2526,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123547348</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2556,6 +2636,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123560721</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2702,6 +2787,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123008823</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2809,6 +2899,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123033899</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2916,6 +3011,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123559251</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3023,6 +3123,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123599090</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3130,6 +3235,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123783535</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3235,6 +3345,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128647344</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3340,6 +3455,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123607777</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3447,6 +3567,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123784683</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3589,6 +3714,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123008173</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3731,6 +3861,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123008919</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3877,6 +4012,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123009266</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4019,6 +4159,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123010595</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4139,6 +4284,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123185939</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4256,6 +4406,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123231344</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4363,6 +4518,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123607303</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4479,6 +4639,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127056116</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4610,6 +4775,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122924019</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4727,6 +4897,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123232797</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4834,6 +5009,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123599223</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4954,6 +5134,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127056859</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5082,6 +5267,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127057091</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5201,6 +5391,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127057216</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5326,6 +5521,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127058829</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5449,6 +5649,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127060592</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5577,6 +5782,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128637642</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5703,6 +5913,11 @@
       <c r="AY43" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128637852</t>
         </is>
       </c>
     </row>
@@ -5806,6 +6021,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123607157</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5907,8 +6127,59 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127056507</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>